--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-08-07-17-25-16-154-TK32</t>
+          <t>DEI-2025-08-22-23-01-22-834-xHv9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-08-07T17:26:03.504235</t>
+          <t>2025-08-22T23:02:09.785328</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-08-07-17-25-15-055-PadT</t>
+          <t>DEI-2025-08-22-23-01-21-543-asUu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-08-07T17:26:03.504683</t>
+          <t>2025-08-22T23:02:09.731688</t>
         </is>
       </c>
     </row>
@@ -552,12 +552,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-08-07-17-25-16-764-DiIU</t>
+          <t>DEI-2025-08-22-23-01-24-012-Ggng</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-08-07T17:26:03.504235</t>
+          <t>2025-08-22T23:02:09.787431</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-08-07-17-25-15-570-s9Yb</t>
+          <t>DEI-2025-08-22-23-01-31-802-xRyS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-08-07T17:26:03.504683</t>
+          <t>2025-08-22T23:02:09.782625</t>
         </is>
       </c>
     </row>
@@ -626,17 +626,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-08-07-17-25-26-137-FUn7</t>
+          <t>DEI-2025-08-22-23-01-26-678-QawY</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-08-07T17:26:03.504070</t>
+          <t>2025-08-22T23:02:09.742275</t>
         </is>
       </c>
     </row>
@@ -663,17 +663,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2025-08-07-17-25-27-230-uhaB</t>
+          <t>DEI-2025-08-22-23-01-32-802-NA8r</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -683,81 +683,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-08-07T17:26:03.504070</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DEI-2025-08-07-17-25-38-342-23wC</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PutawayTaskResult</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2025-08-07T17:26:03.524463</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DEI-2025-08-07-17-25-37-246-GXu8</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PutawayTaskResult</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2025-08-07T17:26:03.506014</t>
+          <t>2025-08-22T23:02:09.787431</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-08-22-23-01-22-834-xHv9</t>
+          <t>DEI-2025-08-24-20-07-58-173-8vt9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-08-22T23:02:09.785328</t>
+          <t>2025-08-24T20:08:48.254087</t>
         </is>
       </c>
     </row>
@@ -515,12 +515,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-08-22-23-01-21-543-asUu</t>
+          <t>DEI-2025-08-24-20-07-59-237-Std4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-08-22T23:02:09.731688</t>
+          <t>2025-08-24T20:08:48.259382</t>
         </is>
       </c>
     </row>
@@ -552,12 +552,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-08-22-23-01-24-012-Ggng</t>
+          <t>DEI-2025-08-24-20-08-09-363-Rxek</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-08-22T23:02:09.787431</t>
+          <t>2025-08-24T20:08:48.259382</t>
         </is>
       </c>
     </row>
@@ -589,17 +589,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-08-22-23-01-31-802-xRyS</t>
+          <t>DEI-2025-08-24-20-08-20-935-OoIC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -609,81 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-08-22T23:02:09.782625</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DEI-2025-08-22-23-01-26-678-QawY</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2025-08-22T23:02:09.742275</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DEI-2025-08-22-23-01-32-802-NA8r</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2025-08-22T23:02:09.787431</t>
+          <t>2025-08-24T20:08:48.256135</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-08-24-20-07-58-173-8vt9</t>
+          <t>DEI-2025-08-25-21-00-52-942-vp6v</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-08-24T20:08:48.254087</t>
+          <t>2025-08-25T21:01:35.630437</t>
         </is>
       </c>
     </row>
@@ -515,17 +515,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-08-24-20-07-59-237-Std4</t>
+          <t>DEI-2025-08-25-21-33-03-445-xwQ8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-08-24T20:08:48.259382</t>
+          <t>2025-08-25T21:33:45.767097</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-08-24-20-08-09-363-Rxek</t>
+          <t>DEI-2025-08-25-21-00-54-831-FkdA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-08-24T20:08:48.259382</t>
+          <t>2025-08-25T21:01:35.630437</t>
         </is>
       </c>
     </row>
@@ -589,27 +589,101 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-08-24-20-08-20-935-OoIC</t>
+          <t>DEI-2025-08-25-21-33-05-656-khgX</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2025-08-25T21:33:45.767097</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEI-2025-08-25-21-33-13-782-i3RO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025-08-25T21:33:45.763857</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEI-2025-08-25-21-33-24-448-5dVu</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>PutawayTaskResult</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2025-08-24T20:08:48.256135</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025-08-25T21:33:45.763857</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-08-25-21-00-52-942-vp6v</t>
+          <t>DEI-2025-09-02-19-45-46-350-hyFh</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-08-25T21:01:35.630437</t>
+          <t>2025-09-02T19:46:27.092120</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-08-25-21-33-03-445-xwQ8</t>
+          <t>DEI-2025-09-02-19-45-47-514-WvlX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-08-25T21:33:45.767097</t>
+          <t>2025-09-02T19:46:27.091720</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-08-25-21-00-54-831-FkdA</t>
+          <t>DEI-2025-09-02-19-45-49-679-MhaQ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-08-25T21:01:35.630437</t>
+          <t>2025-09-02T19:46:27.088829</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-08-25-21-33-05-656-khgX</t>
+          <t>DEI-2025-09-02-19-45-47-186-xGL8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-08-25T21:33:45.767097</t>
+          <t>2025-09-02T19:46:27.091720</t>
         </is>
       </c>
     </row>
@@ -626,17 +626,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-08-25-21-33-13-782-i3RO</t>
+          <t>DEI-2025-09-02-19-50-28-283-MfTp</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>RoutingTaskResult</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-08-25T21:33:45.763857</t>
+          <t>2025-09-02T19:51:17.099005</t>
         </is>
       </c>
     </row>
@@ -663,17 +663,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2025-08-25-21-33-24-448-5dVu</t>
+          <t>DEI-2025-09-02-19-50-27-113-rRW2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>RoutingTaskResult</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-08-25T21:33:45.763857</t>
+          <t>2025-09-02T19:51:17.099005</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-09-02-19-45-46-350-hyFh</t>
+          <t>DEI-2025-09-04-01-23-08-069-fwJI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-09-02T19:46:27.092120</t>
+          <t>2025-09-04T01:23:49.498526</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-09-02-19-45-47-514-WvlX</t>
+          <t>DEI-2025-09-04-01-23-06-882-ZLee</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-09-02T19:46:27.091720</t>
+          <t>2025-09-04T01:23:49.499912</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-09-02-19-45-49-679-MhaQ</t>
+          <t>DEI-2025-09-04-01-23-10-289-pgzn</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-09-02T19:46:27.088829</t>
+          <t>2025-09-04T01:23:49.504970</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-09-02-19-45-47-186-xGL8</t>
+          <t>DEI-2025-09-04-01-23-07-666-osWu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -609,81 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-09-02T19:46:27.091720</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DEI-2025-09-02-19-50-28-283-MfTp</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>RoutingTaskResult</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2025-09-02T19:51:17.099005</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DEI-2025-09-02-19-50-27-113-rRW2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>RoutingTaskResult</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2025-09-02T19:51:17.099005</t>
+          <t>2025-09-04T01:23:49.498526</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-09-04-01-23-08-069-fwJI</t>
+          <t>DEI-2025-09-04-17-22-34-772-CZS7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-09-04T01:23:49.498526</t>
+          <t>2025-09-04T17:22:54.506869</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-09-04-01-23-06-882-ZLee</t>
+          <t>DEI-2025-09-04-17-22-33-592-Sidz</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-09-04T01:23:49.499912</t>
+          <t>2025-09-04T17:22:54.508778</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-09-04-01-23-10-289-pgzn</t>
+          <t>DEI-2025-09-04-17-22-37-547-d82e</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-09-04T01:23:49.504970</t>
+          <t>2025-09-04T17:22:54.506869</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-09-04-01-23-07-666-osWu</t>
+          <t>DEI-2025-09-04-17-22-34-316-IEEz</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -609,7 +609,155 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-09-04T01:23:49.498526</t>
+          <t>2025-09-04T17:22:54.508778</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-04-17-22-44-814-0ID6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025-09-04T17:23:34.494048</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-04-17-22-46-009-mw1x</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025-09-04T17:23:34.494048</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-04-17-22-57-251-3eXF</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2025-09-04T17:23:34.494059</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-04-17-22-56-087-yJje</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025-09-04T17:23:34.494048</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-09-04-17-22-34-772-CZS7</t>
+          <t>DEI-2025-09-11-03-08-51-609-gRSb</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-09-04T17:22:54.506869</t>
+          <t>2025-09-11T03:09:37.320773</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-09-04-17-22-33-592-Sidz</t>
+          <t>DEI-2025-09-11-03-08-50-526-Acw1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-09-04T17:22:54.508778</t>
+          <t>2025-09-11T03:09:37.320773</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-09-04-17-22-37-547-d82e</t>
+          <t>DEI-2025-09-11-03-08-48-209-wTfB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-09-04T17:22:54.506869</t>
+          <t>2025-09-11T03:09:37.321386</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-09-04-17-22-34-316-IEEz</t>
+          <t>DEI-2025-09-11-03-08-48-865-h2hS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -609,155 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-09-04T17:22:54.508778</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DEI-2025-09-04-17-22-44-814-0ID6</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>GoodsholderMeasured</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2025-09-04T17:23:34.494048</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DEI-2025-09-04-17-22-46-009-mw1x</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>GoodsholderMeasured</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2025-09-04T17:23:34.494048</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DEI-2025-09-04-17-22-57-251-3eXF</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PutawayTaskResult</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2025-09-04T17:23:34.494059</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DEI-2025-09-04-17-22-56-087-yJje</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PutawayTaskResult</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2025-09-04T17:23:34.494048</t>
+          <t>2025-09-11T03:09:37.320773</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-09-11-03-08-51-609-gRSb</t>
+          <t>DEI-2025-09-11-19-33-57-577-unAK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-09-11T03:09:37.320773</t>
+          <t>2025-09-11T19:34:46.383625</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-09-11-03-08-50-526-Acw1</t>
+          <t>DEI-2025-09-11-19-21-31-213-oBf5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-09-11T03:09:37.320773</t>
+          <t>2025-09-11T19:22:16.315816</t>
         </is>
       </c>
     </row>
@@ -552,12 +552,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-09-11-03-08-48-209-wTfB</t>
+          <t>DEI-2025-09-11-19-21-31-725-bhDJ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-09-11T03:09:37.321386</t>
+          <t>2025-09-11T19:22:16.315816</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-09-11-03-08-48-865-h2hS</t>
+          <t>DEI-2025-09-11-19-33-59-197-ytM2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -609,7 +609,44 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-09-11T03:09:37.320773</t>
+          <t>2025-09-11T19:34:46.383625</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-11-19-27-33-362-8gb6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025-09-11T19:28:16.323547</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-09-11-19-33-57-577-unAK</t>
+          <t>DEI-2025-09-18-22-14-21-755-vLOC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-09-11T19:34:46.383625</t>
+          <t>2025-09-18T22:15:19.730739</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-09-11-19-21-31-213-oBf5</t>
+          <t>DEI-2025-09-18-22-14-22-951-Tohj</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-09-11T19:22:16.315816</t>
+          <t>2025-09-18T22:15:19.730739</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-09-11-19-21-31-725-bhDJ</t>
+          <t>DEI-2025-09-18-22-14-20-654-L7YK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-09-11T19:22:16.315816</t>
+          <t>2025-09-18T22:15:19.724514</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-09-11-19-33-59-197-ytM2</t>
+          <t>DEI-2025-09-18-22-14-02-474-eVPy</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-09-11T19:34:46.383625</t>
+          <t>2025-09-18T22:14:49.718108</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-09-11-19-27-33-362-8gb6</t>
+          <t>DEI-2025-09-18-22-14-01-281-hLza</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RoutingTaskResult</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -646,7 +646,2264 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-09-11T19:28:16.323547</t>
+          <t>2025-09-18T22:14:49.686507</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-04-784-qsOh</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.732188</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-06-995-C36J</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.769525</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-05-858-MOPC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.763049</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-03-562-fhia</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.730054</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-09-349-ZtLY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.834021</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-08-228-cLUh</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.833551</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-11-674-E34Y</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.875520</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-10-518-nRDj</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.875520</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-16-060-eXji</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.678559</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-12-842-8xbD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.680385</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-13-928-zM1w</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.680385</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-14-999-xwyn</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.679251</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-19-536-wn2Q</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.710492</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-17-211-HT9E</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.702462</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-18-383-CkhO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.705630</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-33-000-2Z4t</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.797668</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-01-978-GQKi</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.688549</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-08-616-6pi6</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.793240</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-08-127-J175</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.833551</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-09-091-ZbRN</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.816773</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-09-516-WOJ8</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.843937</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-12-407-V5U3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.875659</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-09-984-pKu2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:14:49.854509</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-20-029-fIPq</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.710492</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-28-262-DqyQ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.751619</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-27-842-XGbZ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.736428</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-31-741-bCGH</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.753790</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-32-576-L06j</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.785430</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-32-179-2Gdm</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.765493</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-37-347-IhvR</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.724514</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-36-959-9ngk</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.724514</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-36-552-fl7K</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.716652</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-33-535-s99G</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.802259</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-34-282-GQHI</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:49.675922</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-34-713-H1pT</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:49.675282</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-36-108-Ewms</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.710363</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-44-113-TgDQ</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.751619</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-47-496-Tfev</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.753877</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-46-376-UsAK</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.753790</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-45-243-B0sq</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.753170</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-41-862-7Y0H</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.736812</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-42-999-OgfW</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.743372</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-54-306-mNyh</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.785430</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-55-394-Lkfi</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.785430</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-53-239-2MZ3</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.777203</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-48-567-6wbo</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.760268</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-37-285-n3ve</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.724514</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-39-525-Myne</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.736428</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-38-404-6IAO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.735857</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-40-703-sYu9</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.736017</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-33-789-UXHO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:49.675922</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-34-883-5jbg</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:49.677925</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-49-688-zISy</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.762331</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-50-942-pQM6</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.762331</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-14-52-094-3JN4</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:19.772806</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-15-09-275-8jcB</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:49.673903</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-15-11-441-KSdC</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:49.675282</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-15-12-508-Q5G8</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:49.677925</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-15-10-350-BWP4</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:49.679191</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-15-06-997-YzSy</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:49.674880</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-18-22-15-05-887-8EfL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2025-09-18T22:15:49.675922</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-18-50-34-452-YEGo</t>
+          <t>DEI-2025-09-26-20-03-26-263-iXWr</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-09-26T18:51:25.176889</t>
+          <t>2025-09-26T20:04:15.363653</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-19-04-20-214-O44n</t>
+          <t>DEI-2025-09-26-20-03-27-524-faJR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-09-26T19:05:05.045204</t>
+          <t>2025-09-26T20:04:15.363653</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-18-50-39-820-Kaj1</t>
+          <t>DEI-2025-09-26-20-03-29-978-FtWq</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-09-26T18:51:25.176889</t>
+          <t>2025-09-26T20:04:15.400875</t>
         </is>
       </c>
     </row>
@@ -589,27 +589,323 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-19-04-21-471-eHxP</t>
+          <t>DEI-2025-09-26-20-03-28-718-6cCI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2025-09-26T20:04:15.361041</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-26-20-03-31-128-9oYI</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025-09-26T20:04:15.407895</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-26-20-03-32-391-lIcO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025-09-26T20:04:15.427997</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-26-20-03-30-731-reJy</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2025-09-26T19:05:05.045204</t>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2025-09-26T20:04:15.402852</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-26-20-03-32-076-R4b0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025-09-26T20:04:15.427997</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-26-20-03-37-621-ajL5</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2025-09-26T20:04:15.452891</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-26-20-03-41-848-g1Ip</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025-09-26T20:04:15.452891</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-26-20-03-33-231-po7x</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2025-09-26T20:04:15.427997</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DEI-2025-09-26-20-03-36-884-XJg6</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2025-09-26T20:04:15.447559</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-20-03-26-263-iXWr</t>
+          <t>DEI-2025-10-01-21-18-21-292-ACbY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-09-26T20:04:15.363653</t>
+          <t>2025-10-01T21:19:10.050100</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-20-03-27-524-faJR</t>
+          <t>DEI-2025-10-01-21-18-28-139-b1RE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-09-26T20:04:15.363653</t>
+          <t>2025-10-01T21:19:10.108046</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-20-03-29-978-FtWq</t>
+          <t>DEI-2025-10-01-21-18-22-422-US5o</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-09-26T20:04:15.400875</t>
+          <t>2025-10-01T21:19:10.050100</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-20-03-28-718-6cCI</t>
+          <t>DEI-2025-10-01-21-18-25-793-tF5I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-09-26T20:04:15.361041</t>
+          <t>2025-10-01T21:19:10.090620</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-20-03-31-128-9oYI</t>
+          <t>DEI-2025-10-01-21-18-24-673-MkCI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-09-26T20:04:15.407895</t>
+          <t>2025-10-01T21:19:10.086538</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-20-03-32-391-lIcO</t>
+          <t>DEI-2025-10-01-21-18-23-557-CKVm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-09-26T20:04:15.427997</t>
+          <t>2025-10-01T21:19:10.051246</t>
         </is>
       </c>
     </row>
@@ -700,17 +700,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-20-03-30-731-reJy</t>
+          <t>DEI-2025-10-01-21-10-41-798-sfLa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2025-09-26T20:04:15.402852</t>
+          <t>2025-10-01T21:11:30.005119</t>
         </is>
       </c>
     </row>
@@ -737,17 +737,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-20-03-32-076-R4b0</t>
+          <t>DEI-2025-10-01-21-18-26-988-9RFK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2025-09-26T20:04:15.427997</t>
+          <t>2025-10-01T21:19:10.093876</t>
         </is>
       </c>
     </row>
@@ -774,17 +774,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-20-03-37-621-ajL5</t>
+          <t>DEI-2025-10-01-21-10-44-570-k1Md</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2025-09-26T20:04:15.452891</t>
+          <t>2025-10-01T21:11:30.039750</t>
         </is>
       </c>
     </row>
@@ -811,17 +811,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-20-03-41-848-g1Ip</t>
+          <t>DEI-2025-10-01-21-10-43-281-2eyN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2025-09-26T20:04:15.452891</t>
+          <t>2025-10-01T21:11:30.034457</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-20-03-33-231-po7x</t>
+          <t>DEI-2025-10-01-21-10-49-747-VrSJ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2025-09-26T20:04:15.427997</t>
+          <t>2025-10-01T21:11:30.127278</t>
         </is>
       </c>
     </row>
@@ -885,27 +885,1544 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DEI-2025-09-26-20-03-36-884-XJg6</t>
+          <t>DEI-2025-10-01-21-10-46-073-QGaN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:11:30.042636</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-10-50-880-yeVa</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:11:30.129201</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-10-47-281-Nvg7</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:11:30.058542</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-10-48-449-F9Z8</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:11:30.123829</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-10-42-508-wOm9</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2025-09-26T20:04:15.447559</t>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:11:30.007119</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-10-47-561-tIyy</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:11:30.069538</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-10-47-140-zc8F</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:11:30.044870</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-10-59-084-qZKn</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:11:30.157711</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-10-48-009-Cqr4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:11:30.081761</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-10-59-557-QuPJ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:11:59.962051</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-10-51-159-qgP7</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:11:30.131806</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-10-58-629-zbQR</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:11:30.142352</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-18-22-775-g22E</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:19:10.050100</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-18-27-600-4bgq</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:19:10.099057</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-18-35-284-kCn9</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:19:10.144772</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-18-23-658-XIvp</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:19:10.080625</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-18-33-280-HJ0i</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:19:10.135747</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-18-32-457-JpLf</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:19:10.124918</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-18-31-433-K9Gs</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:19:10.119394</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-14-25-042-MPZE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:15:10.001498</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-14-26-176-Exd9</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:15:10.001498</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-14-28-577-BWuw</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:15:10.004243</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-14-29-710-qPOE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:15:10.004243</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-14-30-837-0Hxx</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:15:10.008422</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-14-31-983-NOSs</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:15:10.008422</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-14-27-312-9zfc</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:15:10.004243</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-25-57-731-pBKx</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.046264</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-26-00-034-rJq4</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.045272</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-25-58-853-lvmu</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.046264</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-26-04-623-ikHo</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.047788</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-26-05-796-KG1S</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.047788</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-26-01-225-M7jj</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.045272</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-26-03-472-X9TO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.044121</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-26-02-337-QmdP</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.046310</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-26-16-485-iGPW</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.073360</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-26-23-630-x170</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.096498</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-26-24-791-A8y8</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.097386</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-26-17-680-t5k2</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.073360</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-26-18-934-CYha</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.073360</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-26-20-055-TQ0M</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.073702</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-26-21-185-i2Xk</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.080801</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-01-21-26-22-418-6bHT</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2025-10-01T21:26:40.086614</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-10-08-14-39-02-002-2wpx</t>
+          <t>DEI-2025-10-09-15-50-31-059-XIyS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-10-08T14:39:46.748536</t>
+          <t>2025-10-09T15:51:16.491470</t>
         </is>
       </c>
     </row>
@@ -515,17 +515,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-10-08-14-39-02-526-Ua8i</t>
+          <t>DEI-2025-10-09-15-47-49-610-NKGg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>NO DESTINATION FOUND</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-10-08T14:39:46.750408</t>
+          <t>2025-10-09T15:48:36.475614</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-10-08-14-39-12-329-dZ6Q</t>
+          <t>DEI-2025-10-09-15-50-32-602-ImoF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-10-08T14:39:46.781430</t>
+          <t>2025-10-09T15:51:16.491054</t>
         </is>
       </c>
     </row>
@@ -589,27 +589,138 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-10-08-14-39-22-612-QbnK</t>
+          <t>DEI-2025-10-09-15-50-39-549-wNZ3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2025-10-09T15:51:16.493855</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-09-15-47-57-235-VZDv</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NO DESTINATION FOUND</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025-10-09T15:48:36.475614</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-09-15-50-47-875-MC1m</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>PutawayTaskResult</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2025-10-08T14:39:46.781430</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025-10-09T15:51:16.491361</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-09-15-48-04-916-homV</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NO DESTINATION FOUND</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2025-10-09T15:48:36.473919</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-10-09-15-50-31-059-XIyS</t>
+          <t>DEI-2025-10-14-19-10-06-119-9aLH</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-10-09T15:51:16.491470</t>
+          <t>2025-10-14T19:10:48.200634</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-10-09-15-47-49-610-NKGg</t>
+          <t>DEI-2025-10-14-19-10-07-267-dKSf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-10-09T15:48:36.475614</t>
+          <t>2025-10-14T19:10:48.205072</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-10-09-15-50-32-602-ImoF</t>
+          <t>DEI-2025-10-14-19-10-06-795-zsOf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-10-09T15:51:16.491054</t>
+          <t>2025-10-14T19:10:48.202493</t>
         </is>
       </c>
     </row>
@@ -589,17 +589,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-10-09-15-50-39-549-wNZ3</t>
+          <t>DEI-2025-10-14-19-10-31-309-xzTG</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-10-09T15:51:16.493855</t>
+          <t>2025-10-14T19:10:48.225265</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-10-09-15-47-57-235-VZDv</t>
+          <t>DEI-2025-10-14-19-10-18-545-zawl</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-10-09T15:48:36.475614</t>
+          <t>2025-10-14T19:10:48.204108</t>
         </is>
       </c>
     </row>
@@ -663,12 +663,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2025-10-09-15-50-47-875-MC1m</t>
+          <t>DEI-2025-10-14-19-10-17-417-Cryp</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-10-09T15:51:16.491361</t>
+          <t>2025-10-14T19:10:48.204108</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEI-2025-10-09-15-48-04-916-homV</t>
+          <t>DEI-2025-10-14-19-10-28-778-3qXD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -720,7 +720,44 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2025-10-09T15:48:36.473919</t>
+          <t>2025-10-14T19:10:48.205072</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-14-19-10-29-890-t4Sh</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025-10-14T19:10:48.225265</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-10-14-19-10-06-119-9aLH</t>
+          <t>DEI-2025-10-23-20-45-08-182-WfzJ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-10-14T19:10:48.200634</t>
+          <t>2025-10-23T20:45:49.400881</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-10-14-19-10-07-267-dKSf</t>
+          <t>DEI-2025-10-23-21-02-33-412-QkiJ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-10-14T19:10:48.205072</t>
+          <t>2025-10-23T21:03:19.491025</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-10-14-19-10-06-795-zsOf</t>
+          <t>DEI-2025-10-23-20-29-53-435-PITu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-10-14T19:10:48.202493</t>
+          <t>2025-10-23T20:30:39.356328</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-10-14-19-10-31-309-xzTG</t>
+          <t>DEI-2025-10-23-20-29-54-911-NSM8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-10-14T19:10:48.225265</t>
+          <t>2025-10-23T20:30:39.356333</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-10-14-19-10-18-545-zawl</t>
+          <t>DEI-2025-10-23-20-45-11-052-HLEm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-10-14T19:10:48.204108</t>
+          <t>2025-10-23T20:45:49.400422</t>
         </is>
       </c>
     </row>
@@ -663,12 +663,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2025-10-14-19-10-17-417-Cryp</t>
+          <t>DEI-2025-10-23-21-02-35-809-9HZv</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-10-14T19:10:48.204108</t>
+          <t>2025-10-23T21:03:19.489803</t>
         </is>
       </c>
     </row>
@@ -700,12 +700,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEI-2025-10-14-19-10-28-778-3qXD</t>
+          <t>DEI-2025-10-23-20-35-48-398-BwF4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>RoutingTaskResult</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2025-10-14T19:10:48.205072</t>
+          <t>2025-10-23T20:36:29.348961</t>
         </is>
       </c>
     </row>
@@ -737,27 +737,101 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEI-2025-10-14-19-10-29-890-t4Sh</t>
+          <t>DEI-2025-10-23-20-57-15-705-LJij</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025-10-23T20:57:59.450557</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-23-21-11-16-391-MBss</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SSHR21</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2025-10-23T21:11:29.530669</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEI-2025-10-23-21-11-26-848-YGUm</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>PutawayTaskResult</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2025-10-14T19:10:48.225265</t>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025-10-23T21:12:09.519636</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-10-23-20-45-08-182-WfzJ</t>
+          <t>DEI-2025-10-31-18-17-40-366-a7M7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-10-23T20:45:49.400881</t>
+          <t>2025-10-31T18:18:24.122509</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-10-23-21-02-33-412-QkiJ</t>
+          <t>DEI-2025-10-31-18-17-41-548-eQv8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-10-23T21:03:19.491025</t>
+          <t>2025-10-31T18:18:24.122509</t>
         </is>
       </c>
     </row>
@@ -552,12 +552,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-10-23-20-29-53-435-PITu</t>
+          <t>DEI-2025-10-31-18-17-41-186-5r65</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-10-23T20:30:39.356328</t>
+          <t>2025-10-31T18:18:24.122509</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-10-23-20-29-54-911-NSM8</t>
+          <t>DEI-2025-10-31-18-17-43-141-r1wc</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-10-23T20:30:39.356333</t>
+          <t>2025-10-31T18:18:24.123308</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-10-23-20-45-11-052-HLEm</t>
+          <t>DEI-2025-10-31-18-17-52-155-ans7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-10-23T20:45:49.400422</t>
+          <t>2025-10-31T18:18:24.126734</t>
         </is>
       </c>
     </row>
@@ -663,12 +663,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2025-10-23-21-02-35-809-9HZv</t>
+          <t>DEI-2025-10-31-18-17-53-454-u96P</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-10-23T21:03:19.489803</t>
+          <t>2025-10-31T18:18:24.126734</t>
         </is>
       </c>
     </row>
@@ -700,12 +700,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEI-2025-10-23-20-35-48-398-BwF4</t>
+          <t>DEI-2025-10-31-18-18-04-034-kogu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RoutingTaskResult</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2025-10-23T20:36:29.348961</t>
+          <t>2025-10-31T18:18:24.125966</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEI-2025-10-23-20-57-15-705-LJij</t>
+          <t>DEI-2025-10-31-18-18-05-297-V0hy</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RoutingTaskResult</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -757,81 +757,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2025-10-23T20:57:59.450557</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>DEI-2025-10-23-21-11-16-391-MBss</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>GoodsholderMeasured</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SSHR21</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2025-10-23T21:11:29.530669</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>DEI-2025-10-23-21-11-26-848-YGUm</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>PutawayTaskResult</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2025-10-23T21:12:09.519636</t>
+          <t>2025-10-31T18:18:24.124816</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-10-31-18-17-40-366-a7M7</t>
+          <t>DEI-2025-11-07-20-33-37-719-RGng</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-10-31T18:18:24.122509</t>
+          <t>2025-11-07T20:34:22.368393</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-10-31-18-17-41-548-eQv8</t>
+          <t>DEI-2025-11-07-20-33-36-536-VW8r</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-10-31T18:18:24.122509</t>
+          <t>2025-11-07T20:34:22.354499</t>
         </is>
       </c>
     </row>
@@ -552,12 +552,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-10-31-18-17-41-186-5r65</t>
+          <t>DEI-2025-11-07-20-33-35-348-ZZZe</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-10-31T18:18:24.122509</t>
+          <t>2025-11-07T20:34:22.330864</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-10-31-18-17-43-141-r1wc</t>
+          <t>DEI-2025-11-07-20-33-40-095-lNql</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-10-31T18:18:24.123308</t>
+          <t>2025-11-07T20:34:22.372112</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-10-31-18-17-52-155-ans7</t>
+          <t>DEI-2025-11-07-20-33-38-907-ni0M</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-10-31T18:18:24.126734</t>
+          <t>2025-11-07T20:34:22.373507</t>
         </is>
       </c>
     </row>
@@ -663,12 +663,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2025-10-31-18-17-53-454-u96P</t>
+          <t>DEI-2025-11-07-20-33-41-236-ZBdb</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-10-31T18:18:24.126734</t>
+          <t>2025-11-07T20:34:22.381787</t>
         </is>
       </c>
     </row>
@@ -700,12 +700,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEI-2025-10-31-18-18-04-034-kogu</t>
+          <t>DEI-2025-11-07-20-33-44-768-XcOw</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2025-10-31T18:18:24.125966</t>
+          <t>2025-11-07T20:34:22.400610</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEI-2025-10-31-18-18-05-297-V0hy</t>
+          <t>DEI-2025-11-07-20-33-43-606-5y1Z</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -757,7 +757,414 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2025-10-31T18:18:24.124816</t>
+          <t>2025-11-07T20:34:22.395769</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-07-20-33-42-432-riVC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2025-11-07T20:34:22.405454</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-07-20-33-38-505-qxDU</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025-11-07T20:34:22.330644</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-07-20-33-37-320-13B8</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2025-11-07T20:34:22.329441</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-07-20-33-35-955-Gq5e</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2025-11-07T20:34:22.321968</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-07-20-33-39-771-o40G</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2025-11-07T20:34:22.358156</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-07-20-33-41-681-4Npm</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2025-11-07T20:34:22.372112</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-07-20-33-45-497-SSc3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2025-11-07T20:34:22.400610</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-07-20-33-44-814-UOW2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2025-11-07T20:34:22.400610</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-07-20-33-42-136-kG8y</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2025-11-07T20:34:22.381787</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-07-20-33-39-859-hmuC</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2025-11-07T20:34:22.362622</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-07-20-33-43-575-oRKR</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2025-11-07T20:34:22.386507</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-11-07-20-33-37-719-RGng</t>
+          <t>DEI-2025-11-14-00-57-56-663-eJN4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-11-07T20:34:22.368393</t>
+          <t>2025-11-14T00:58:38.953260</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-11-07-20-33-36-536-VW8r</t>
+          <t>DEI-2025-11-14-01-00-52-525-Norw</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-11-07T20:34:22.354499</t>
+          <t>2025-11-14T01:01:38.956934</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-11-07-20-33-35-348-ZZZe</t>
+          <t>DEI-2025-11-14-00-57-55-788-JNHk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-11-07T20:34:22.330864</t>
+          <t>2025-11-14T00:58:38.951463</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-11-07-20-33-40-095-lNql</t>
+          <t>DEI-2025-11-14-00-57-57-589-zbtP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-11-07T20:34:22.372112</t>
+          <t>2025-11-14T00:58:38.953260</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-11-07-20-33-38-907-ni0M</t>
+          <t>DEI-2025-11-14-00-57-56-499-KEW5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-11-07T20:34:22.373507</t>
+          <t>2025-11-14T00:58:38.951463</t>
         </is>
       </c>
     </row>
@@ -663,12 +663,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2025-11-07-20-33-41-236-ZBdb</t>
+          <t>DEI-2025-11-14-01-01-20-115-AxVv</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-11-07T20:34:22.381787</t>
+          <t>2025-11-14T01:01:38.956934</t>
         </is>
       </c>
     </row>
@@ -700,12 +700,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEI-2025-11-07-20-33-44-768-XcOw</t>
+          <t>DEI-2025-11-14-00-59-20-227-YJMx</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>RoutingTaskResult</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2025-11-07T20:34:22.400610</t>
+          <t>2025-11-14T01:00:08.955623</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEI-2025-11-07-20-33-43-606-5y1Z</t>
+          <t>DEI-2025-11-14-01-03-13-676-zzoR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2025-11-07T20:34:22.395769</t>
+          <t>2025-11-14T01:03:58.975339</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DEI-2025-11-07-20-33-42-432-riVC</t>
+          <t>DEI-2025-11-14-01-03-14-603-kqZw</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2025-11-07T20:34:22.405454</t>
+          <t>2025-11-14T01:03:58.975339</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DEI-2025-11-07-20-33-38-505-qxDU</t>
+          <t>DEI-2025-11-14-01-03-24-520-OBQ8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2025-11-07T20:34:22.330644</t>
+          <t>2025-11-14T01:03:58.976244</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DEI-2025-11-07-20-33-37-320-13B8</t>
+          <t>DEI-2025-11-14-01-03-23-696-7Zej</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -868,303 +868,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2025-11-07T20:34:22.329441</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-07-20-33-35-955-Gq5e</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2025-11-07T20:34:22.321968</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-07-20-33-39-771-o40G</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2025-11-07T20:34:22.358156</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-07-20-33-41-681-4Npm</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2025-11-07T20:34:22.372112</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-07-20-33-45-497-SSc3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2025-11-07T20:34:22.400610</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-07-20-33-44-814-UOW2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2025-11-07T20:34:22.400610</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-07-20-33-42-136-kG8y</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2025-11-07T20:34:22.381787</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-07-20-33-39-859-hmuC</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2025-11-07T20:34:22.362622</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-07-20-33-43-575-oRKR</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2025-11-07T20:34:22.386507</t>
+          <t>2025-11-14T01:03:58.976244</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-11-14-00-57-56-663-eJN4</t>
+          <t>DEI-2025-11-26-01-04-08-213-3YMb</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-11-14T00:58:38.953260</t>
+          <t>2025-11-26T01:06:18.578025</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-11-14-01-00-52-525-Norw</t>
+          <t>DEI-2025-11-26-01-04-07-296-u8rf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-11-14T01:01:38.956934</t>
+          <t>2025-11-26T01:04:48.601772</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-11-14-00-57-55-788-JNHk</t>
+          <t>DEI-2025-11-26-01-04-08-154-PtY4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-11-14T00:58:38.951463</t>
+          <t>2025-11-26T01:06:18.576595</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-11-14-00-57-57-589-zbtP</t>
+          <t>DEI-2025-11-26-01-05-32-038-WnBw</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-11-14T00:58:38.953260</t>
+          <t>2025-11-26T01:07:38.560351</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-11-14-00-57-56-499-KEW5</t>
+          <t>DEI-2025-11-26-01-29-09-530-vhrs</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>RoutingTaskResult</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-11-14T00:58:38.951463</t>
+          <t>2025-11-26T01:29:58.674513</t>
         </is>
       </c>
     </row>
@@ -663,12 +663,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2025-11-14-01-01-20-115-AxVv</t>
+          <t>DEI-2025-11-26-01-29-10-443-Opsz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>RoutingTaskResult</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -683,192 +683,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-11-14T01:01:38.956934</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-14-00-59-20-227-YJMx</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>RoutingTaskResult</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2025-11-14T01:00:08.955623</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-14-01-03-13-676-zzoR</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>GoodsholderMeasured</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2025-11-14T01:03:58.975339</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-14-01-03-14-603-kqZw</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>GoodsholderMeasured</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2025-11-14T01:03:58.975339</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-14-01-03-24-520-OBQ8</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>PutawayTaskResult</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2025-11-14T01:03:58.976244</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-14-01-03-23-696-7Zej</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>PutawayTaskResult</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2025-11-14T01:03:58.976244</t>
+          <t>2025-11-26T01:29:58.674513</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-11-26-01-04-08-213-3YMb</t>
+          <t>DEI-2025-11-26-20-47-47-065-WiCu</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-11-26T01:06:18.578025</t>
+          <t>2025-11-26T20:48:34.444724</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-11-26-01-04-07-296-u8rf</t>
+          <t>DEI-2025-11-26-20-47-47-946-trmk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-11-26T01:04:48.601772</t>
+          <t>2025-11-26T20:48:34.444724</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-11-26-01-04-08-154-PtY4</t>
+          <t>DEI-2025-11-26-18-31-24-422-gt1c</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-11-26T01:06:18.576595</t>
+          <t>2025-11-26T18:32:13.779243</t>
         </is>
       </c>
     </row>
@@ -589,17 +589,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-11-26-01-05-32-038-WnBw</t>
+          <t>DEI-2025-11-26-18-31-25-316-SVJ9</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-11-26T01:07:38.560351</t>
+          <t>2025-11-26T18:32:13.778606</t>
         </is>
       </c>
     </row>
@@ -626,17 +626,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-11-26-01-29-09-530-vhrs</t>
+          <t>DEI-2025-11-26-18-31-26-421-yxb5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RoutingTaskResult</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-11-26T01:29:58.674513</t>
+          <t>2025-11-26T18:33:33.764645</t>
         </is>
       </c>
     </row>
@@ -663,27 +663,323 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2025-11-26-01-29-10-443-Opsz</t>
+          <t>DEI-2025-11-26-18-31-27-326-aA8P</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025-11-26T18:34:53.798395</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-26-20-47-48-208-M1kD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2025-11-26T20:49:54.439024</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-26-20-47-49-103-JZmj</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025-11-26T20:51:14.447019</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-26-18-35-42-722-dOc5</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>RoutingTaskResult</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2025-11-26T01:29:58.674513</t>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2025-11-26T18:36:23.775511</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-26-18-35-41-833-5pXL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025-11-26T18:36:23.775511</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-26-20-56-07-258-ySEJ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2025-11-26T20:56:54.478557</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-26-20-56-08-178-SNcp</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2025-11-26T20:56:54.480556</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-26-20-56-16-985-SicQ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2025-11-26T20:56:54.481940</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DEI-2025-11-26-20-56-17-855-Xzmd</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2025-11-26T20:56:54.481940</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-11-26-20-47-47-065-WiCu</t>
+          <t>DEI-2025-12-03-02-04-44-896-iCHX</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-11-26T20:48:34.444724</t>
+          <t>2025-12-03T02:05:33.805761</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-11-26-20-47-47-946-trmk</t>
+          <t>DEI-2025-12-03-02-04-44-512-qnmo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-11-26T20:48:34.444724</t>
+          <t>2025-12-03T02:05:33.805761</t>
         </is>
       </c>
     </row>
@@ -552,12 +552,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-11-26-18-31-24-422-gt1c</t>
+          <t>DEI-2025-12-03-02-04-46-047-1uGo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-11-26T18:32:13.779243</t>
+          <t>2025-12-03T02:05:33.805761</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-11-26-18-31-25-316-SVJ9</t>
+          <t>DEI-2025-12-03-02-04-47-357-RF1a</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -609,377 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-11-26T18:32:13.778606</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-26-18-31-26-421-yxb5</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2025-11-26T18:33:33.764645</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-26-18-31-27-326-aA8P</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2025-11-26T18:34:53.798395</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-26-20-47-48-208-M1kD</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2025-11-26T20:49:54.439024</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-26-20-47-49-103-JZmj</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PTW_DEI_AllocationCreated</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2025-11-26T20:51:14.447019</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-26-18-35-42-722-dOc5</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>RoutingTaskResult</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2025-11-26T18:36:23.775511</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-26-18-35-41-833-5pXL</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>RoutingTaskResult</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2025-11-26T18:36:23.775511</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-26-20-56-07-258-ySEJ</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>GoodsholderMeasured</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2025-11-26T20:56:54.478557</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-26-20-56-08-178-SNcp</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>GoodsholderMeasured</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2025-11-26T20:56:54.480556</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-26-20-56-16-985-SicQ</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PutawayTaskResult</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2025-11-26T20:56:54.481940</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>DEI-2025-11-26-20-56-17-855-Xzmd</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PutawayTaskResult</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2025-11-26T20:56:54.481940</t>
+          <t>2025-12-03T02:05:33.806400</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,20 +446,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>LPN_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Message_Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Created_on</t>
         </is>
@@ -478,27 +483,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-12-03-02-04-44-896-iCHX</t>
+          <t>DEI-2025-12-05-07-03-13-804-bwtc</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>20251204224646000002</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>GoodsholderAnnounced</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-12-03T02:05:33.805761</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-12-05T07:03:43.215331</t>
         </is>
       </c>
     </row>
@@ -515,27 +525,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-12-03-02-04-44-512-qnmo</t>
+          <t>DEI-2025-12-05-07-03-28-181-0bek</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>20251204224646000001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>GoodsholderAnnounced</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-12-03T02:05:33.805761</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2025-12-05T07:04:13.202174</t>
         </is>
       </c>
     </row>
@@ -552,27 +567,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-12-03-02-04-46-047-1uGo</t>
+          <t>DEI-2025-12-05-07-03-59-665-7UCP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>20251204224646000002</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>RoutingTaskResult</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-12-03T02:05:33.805761</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-12-05T07:04:43.207780</t>
         </is>
       </c>
     </row>
@@ -589,27 +609,368 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-12-03-02-04-47-357-RF1a</t>
+          <t>DEI-2025-12-05-07-04-13-424-3jdF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>20251204224646000001</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>RoutingTaskResult</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-12-03T02:05:33.806400</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-12-05T07:04:43.207780</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-07-11-15-929-06LA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20251204224646000001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-12-05T07:11:43.245072</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-07-11-01-134-6bL8</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20251204224646000002</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-12-05T07:11:43.246215</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-07-12-02-683-uVQp</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20251204224646000001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-12-05T07:12:43.241004</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-07-13-30-382-Cszh</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20251204224646000002</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2025-12-05T07:14:13.249415</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-07-17-09-374-iLzm</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20251204224646000002</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-12-05T07:17:53.273994</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-07-17-25-945-vZ5K</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20251204224646000001</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025-12-05T07:17:53.277066</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-07-19-54-926-diMw</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20251204224646000001</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025-12-05T07:20:43.285144</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-07-23-39-965-Xp8j</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20251204224646000001</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2025-12-05T07:24:23.297789</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,20 +451,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Lock</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Message_Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Created_on</t>
         </is>
@@ -483,32 +488,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-12-05-07-03-13-804-bwtc</t>
+          <t>DEI-2025-12-10-06-10-45-529-C3Lb</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20251204224646000002</t>
+          <t>00009369430000189413</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>GoodsholderAnnounced</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-12-05T07:03:43.215331</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:11:35.469159</t>
         </is>
       </c>
     </row>
@@ -525,32 +535,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-12-05-07-03-28-181-0bek</t>
+          <t>DEI-2025-12-10-06-10-46-169-DW70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20251204224646000001</t>
+          <t>00009369430000189413</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-12-05T07:04:13.202174</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:11:35.469159</t>
         </is>
       </c>
     </row>
@@ -567,32 +582,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-12-05-07-03-59-665-7UCP</t>
+          <t>DEI-2025-12-10-06-13-14-817-0dBq</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20251204224646000002</t>
+          <t>00009369430000189413</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RoutingTaskResult</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-12-05T07:04:43.207780</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:13:55.474611</t>
         </is>
       </c>
     </row>
@@ -609,32 +629,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-12-05-07-04-13-424-3jdF</t>
+          <t>DEI-2025-12-10-06-14-27-722-2wta</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20251204224646000001</t>
+          <t>00009369430000189413</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RoutingTaskResult</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2025-12-05T07:04:43.207780</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:15:15.494649</t>
         </is>
       </c>
     </row>
@@ -651,32 +676,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-12-05-07-11-15-929-06LA</t>
+          <t>DEI-2025-12-10-06-27-38-679-jNtr</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20251204224646000001</t>
+          <t>00009369430000189413</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>DCI_DEI_RemoveConditionCode</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>NO DESTINATION FOUND</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2025-12-05T07:11:43.245072</t>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:28:25.544136</t>
         </is>
       </c>
     </row>
@@ -693,32 +723,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2025-12-05-07-11-01-134-6bL8</t>
+          <t>DEI-2025-12-10-06-11-38-736-Kc2Y</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20251204224646000002</t>
+          <t>00018335030000996223</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>GoodsholderAnnounced</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2025-12-05T07:11:43.246215</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:12:05.483414</t>
         </is>
       </c>
     </row>
@@ -735,32 +770,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEI-2025-12-05-07-12-02-683-uVQp</t>
+          <t>DEI-2025-12-10-06-11-39-161-5xBi</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20251204224646000001</t>
+          <t>00018335030000996223</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RoutingTaskResult</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2025-12-05T07:12:43.241004</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:12:05.483414</t>
         </is>
       </c>
     </row>
@@ -777,32 +817,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEI-2025-12-05-07-13-30-382-Cszh</t>
+          <t>DEI-2025-12-10-06-14-08-210-1aNO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20251204224646000002</t>
+          <t>00018335030000996223</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>GoodsholderMeasured</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2025-12-05T07:14:13.249415</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:14:35.479104</t>
         </is>
       </c>
     </row>
@@ -819,32 +864,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DEI-2025-12-05-07-17-09-374-iLzm</t>
+          <t>DEI-2025-12-10-06-15-21-417-4URO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20251204224646000002</t>
+          <t>00018335030000996223</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>PutawayTaskResult</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2025-12-05T07:17:53.273994</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:15:45.489471</t>
         </is>
       </c>
     </row>
@@ -861,32 +911,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DEI-2025-12-05-07-17-25-945-vZ5K</t>
+          <t>DEI-2025-12-10-06-40-52-658-k72K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20251204224646000001</t>
+          <t>00018335030000996223</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>DCI_DEI_RemoveConditionCode</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>NO DESTINATION FOUND</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2025-12-05T07:17:53.277066</t>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:41:35.627720</t>
         </is>
       </c>
     </row>
@@ -903,32 +958,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DEI-2025-12-05-07-19-54-926-diMw</t>
+          <t>DEI-2025-12-10-06-11-18-815-ZgTs</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20251204224646000001</t>
+          <t>00027112400000181326</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2025-12-05T07:20:43.285144</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:12:05.478673</t>
         </is>
       </c>
     </row>
@@ -945,32 +1005,1588 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DEI-2025-12-05-07-23-39-965-Xp8j</t>
+          <t>DEI-2025-12-10-06-11-19-250-pNrg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20251204224646000001</t>
+          <t>00027112400000181326</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:12:05.478673</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-13-47-642-1Rhw</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00027112400000181326</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:14:35.479104</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-15-00-964-Uxa4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00027112400000181326</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>PutawayTaskResult</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2025-12-05T07:24:23.297789</t>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:15:45.491490</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-37-58-196-ZhX2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00027112400000181326</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NO DESTINATION FOUND</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:38:45.601909</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-11-15-642-NKki</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00033324160000421528</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:12:05.480887</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-11-16-118-g10l</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00033324160000421528</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:12:05.480887</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-13-44-483-5oCD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00033324160000421528</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:13:55.474611</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-14-57-807-O9h7</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00033324160000421528</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:15:45.490095</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-37-20-379-sfbN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00033324160000421528</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NO DESTINATION FOUND</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:38:05.597367</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-12-06-853-67AK</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00048562010000569466</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:12:55.471986</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-12-07-313-28N6</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00048562010000569466</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:12:55.471986</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-14-35-953-Gz4w</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00048562010000569466</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:15:15.494649</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-15-48-959-fydr</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00048562010000569466</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:16:35.493492</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-21-30-296-B5LR</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00048562010000569466</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NO DESTINATION FOUND</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:22:15.525049</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-49-36-303-SHYn</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>T4121020250000000004</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:50:25.681008</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-49-39-247-z4TH</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>T4121020250000000004</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:50:25.682394</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-51-57-176-9Bgm</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>T4121020250000000004</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>NO DESTINATION FOUND</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:52:45.668203</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-55-50-119-n854</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>T4121020250000000004</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:56:25.709437</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-49-38-844-aqCP</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>T4121020250000000005</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:50:25.682394</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-49-41-308-Ujwb</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>T4121020250000000005</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:50:25.682394</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-51-59-730-acUR</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>T4121020250000000005</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NO DESTINATION FOUND</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:52:45.668942</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-55-39-228-DR0O</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>T4121020250000000005</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:56:25.709640</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-49-43-953-pp5J</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>T4121020250000000006</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:50:25.681059</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-49-41-949-A6s3</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>T4121020250000000006</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:50:25.683402</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-52-02-856-OQBU</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>T4121020250000000006</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>NO DESTINATION FOUND</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:52:45.668942</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-55-49-514-cHcu</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>T4121020250000000006</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:56:25.710122</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-49-45-109-1Z0O</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>T4121020250000000007</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:50:25.681059</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-49-47-121-HjhM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>T4121020250000000007</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:50:25.683004</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-52-05-998-Hzuw</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>T4121020250000000007</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NO DESTINATION FOUND</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:52:45.669783</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-55-42-267-e1NB</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>T4121020250000000007</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:56:25.710122</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-49-48-249-U0h1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>T4121020250000000008</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:50:25.683004</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-49-49-021-BjUl</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>T4121020250000000008</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:50:25.710870</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-52-09-153-BuBK</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>T4121020250000000008</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>NO DESTINATION FOUND</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:52:45.669783</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-10-06-55-50-769-fwPH</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>T4121020250000000008</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:56:25.709437</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,27 +451,27 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Message_Type</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Message_Type</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>User</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Created_on</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Created_on</t>
+          <t>RSN_CODE</t>
         </is>
       </c>
     </row>
@@ -488,37 +488,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-10-45-529-C3Lb</t>
+          <t>DEI-2025-12-10-08-00-38-719-kp8D</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00009369430000189413</t>
+          <t>00000010810000000008</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-10T08:01:21.123721</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2025-12-10T06:11:35.469159</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -535,37 +535,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-10-46-169-DW70</t>
+          <t>DEI-2025-12-11-08-48-18-032-1lLc</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00009369430000189413</t>
+          <t>00008866681787844840</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>DUPLICATE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T08:49:07.660042</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2025-12-10T06:11:35.469159</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -582,37 +582,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-13-14-817-0dBq</t>
+          <t>DEI-2025-12-11-08-50-26-045-1BuA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00009369430000189413</t>
+          <t>00008866681787844840</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>DUPLICATE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T08:51:07.676971</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2025-12-10T06:13:55.474611</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -629,37 +629,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-14-27-722-2wta</t>
+          <t>DEI-2025-12-11-02-14-28-261-zpeZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00009369430000189413</t>
+          <t>00012050590000845698</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T02:14:59.177845</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2025-12-10T06:15:15.494649</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -676,37 +676,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-27-38-679-jNtr</t>
+          <t>DEI-2025-12-04-10-57-09-487-hSIb</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00009369430000189413</t>
+          <t>10812025120411481001</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DCI_DEI_RemoveConditionCode</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>hdutta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>2025-12-04T10:57:53.058439</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2025-12-10T06:28:25.544136</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -723,37 +723,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-11-38-736-Kc2Y</t>
+          <t>DEI-2025-12-11-00-57-12-598-4ezp</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00018335030000996223</t>
+          <t>20201211000000000001</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>NO DESTINATION FOUND</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T00:57:58.708653</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2025-12-10T06:12:05.483414</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -770,37 +770,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-11-39-161-5xBi</t>
+          <t>DEI-2025-12-03-06-52-48-000-6jW8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00018335030000996223</t>
+          <t>20251202191347000004</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>NO DESTINATION FOUND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-03T06:53:35.361445</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2025-12-10T06:12:05.483414</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -817,37 +817,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-14-08-210-1aNO</t>
+          <t>DEI-2025-12-11-20-20-26-164-OhfU</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00018335030000996223</t>
+          <t>20251203004902000012</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:21:06.704884</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2025-12-10T06:14:35.479104</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -864,37 +864,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-15-21-417-4URO</t>
+          <t>DEI-2025-12-11-21-05-49-599-2bXh</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00018335030000996223</t>
+          <t>20251203004902000013</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T21:06:16.934225</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2025-12-10T06:15:45.489471</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -911,37 +911,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-40-52-658-k72K</t>
+          <t>DEI-2025-12-11-20-35-30-171-7fDw</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00018335030000996223</t>
+          <t>20251203004902000014</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DCI_DEI_RemoveConditionCode</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>ASure2</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>2025-12-11T20:36:16.806945</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2025-12-10T06:41:35.627720</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -958,37 +958,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-11-18-815-ZgTs</t>
+          <t>DEI-2025-12-11-20-20-36-027-nWIl</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00027112400000181326</t>
+          <t>20251203004902000015</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:21:06.706123</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2025-12-10T06:12:05.478673</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1005,37 +1005,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-11-19-250-pNrg</t>
+          <t>DEI-2025-12-11-20-35-40-182-RuLy</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00027112400000181326</t>
+          <t>20251203004902000017</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:36:16.806630</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2025-12-10T06:12:05.478673</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1052,37 +1052,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-13-47-642-1Rhw</t>
+          <t>DEI-2025-12-11-20-35-48-373-E1GW</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>00027112400000181326</t>
+          <t>20251203004902000019</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:36:16.806630</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2025-12-10T06:14:35.479104</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1099,37 +1099,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-15-00-964-Uxa4</t>
+          <t>DEI-2025-12-04-04-41-31-533-12c5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>00027112400000181326</t>
+          <t>20251203165151000001</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-04T04:42:18.984928</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2025-12-10T06:15:45.491490</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1146,37 +1146,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-37-58-196-ZhX2</t>
+          <t>DEI-2025-12-04-04-48-14-008-cLFb</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>00027112400000181326</t>
+          <t>20251203165151000001</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DCI_DEI_RemoveConditionCode</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>2025-12-04T04:48:49.010508</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2025-12-10T06:38:45.601909</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1193,37 +1193,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-11-15-642-NKki</t>
+          <t>DEI-2025-12-04-13-47-38-982-uNq5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>00033324160000421528</t>
+          <t>20251203165151000002</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>ndatch</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-04T13:48:19.738024</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2025-12-10T06:12:05.480887</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1240,37 +1240,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-11-16-118-g10l</t>
+          <t>DEI-2025-12-04-13-56-44-388-DiVv</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>00033324160000421528</t>
+          <t>20251203165151000003</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>NO DESTINATION FOUND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>ndatch</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-04T13:57:29.765725</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2025-12-10T06:12:05.480887</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1287,37 +1287,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-13-44-483-5oCD</t>
+          <t>DEI-2025-12-05-04-31-45-568-nnWi</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>00033324160000421528</t>
+          <t>20251203183845000000</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>NO DESTINATION FOUND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-05T04:32:18.137593</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2025-12-10T06:13:55.474611</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1334,37 +1334,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-14-57-807-O9h7</t>
+          <t>DEI-2025-12-05-04-25-06-783-W2KJ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>00033324160000421528</t>
+          <t>20251204180041000000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>NO DESTINATION FOUND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-05T04:25:38.101129</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2025-12-10T06:15:45.490095</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1381,37 +1381,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-37-20-379-sfbN</t>
+          <t>DEI-2025-12-10-00-38-06-104-DytA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>00033324160000421528</t>
+          <t>20251207131832000001</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DCI_DEI_RemoveConditionCode</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>2025-12-10T00:38:42.153489</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2025-12-10T06:38:05.597367</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1428,37 +1428,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-12-06-853-67AK</t>
+          <t>DEI-2025-12-11-20-35-33-856-2gQy</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>00048562010000569466</t>
+          <t>20251207131832000001</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:36:16.800111</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2025-12-10T06:12:55.471986</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1475,37 +1475,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-12-07-313-28N6</t>
+          <t>DEI-2025-12-11-20-35-53-667-exDU</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>00048562010000569466</t>
+          <t>20251207131832000002</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:36:16.808269</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2025-12-10T06:12:55.471986</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1522,37 +1522,37 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-14-35-953-Gz4w</t>
+          <t>DEI-2025-12-10-00-38-21-151-sSDH</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>00048562010000569466</t>
+          <t>20251207131832000003</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>NO DESTINATION FOUND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-10T00:38:42.153489</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2025-12-10T06:15:15.494649</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1569,37 +1569,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-15-48-959-fydr</t>
+          <t>DEI-2025-12-11-20-20-38-638-F2OL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>00048562010000569466</t>
+          <t>20251207132608000001</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:21:06.706123</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2025-12-10T06:16:35.493492</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1616,37 +1616,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-21-30-296-B5LR</t>
+          <t>DEI-2025-12-11-20-35-38-540-FM8z</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>00048562010000569466</t>
+          <t>20251207132608000002</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>DCI_DEI_RemoveConditionCode</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>2025-12-11T20:36:16.800111</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2025-12-10T06:22:15.525049</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1663,37 +1663,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-49-36-303-SHYn</t>
+          <t>DEI-2025-12-11-20-20-51-045-V7Lu</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>T4121020250000000004</t>
+          <t>20251207132608000003</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:21:06.703923</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2025-12-10T06:50:25.681008</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1710,37 +1710,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-49-39-247-z4TH</t>
+          <t>DEI-2025-12-11-20-35-54-784-UmgJ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>T4121020250000000004</t>
+          <t>20251207132608000004</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:36:16.827088</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2025-12-10T06:50:25.682394</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1757,37 +1757,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-51-57-176-9Bgm</t>
+          <t>DEI-2025-12-11-05-54-29-196-uHy3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>T4121020250000000004</t>
+          <t>20251207165309000002</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T05:55:12.950016</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2025-12-10T06:52:45.668203</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1804,37 +1804,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-55-50-119-n854</t>
+          <t>DEI-2025-12-12-01-50-25-822-2Dky</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>T4121020250000000004</t>
+          <t>20251208005024000004</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-12T01:51:09.813482</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2025-12-10T06:56:25.709437</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1851,37 +1851,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-49-38-844-aqCP</t>
+          <t>DEI-2025-12-11-21-05-36-636-diXC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>T4121020250000000005</t>
+          <t>20251208173045000021</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T21:06:16.933335</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2025-12-10T06:50:25.682394</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1898,37 +1898,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-49-41-308-Ujwb</t>
+          <t>DEI-2025-12-11-21-05-45-405-N7mf</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>T4121020250000000005</t>
+          <t>20251208173045000024</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T21:06:16.934225</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2025-12-10T06:50:25.682394</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1945,37 +1945,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-51-59-730-acUR</t>
+          <t>DEI-2025-12-11-21-05-30-306-8SBt</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>T4121020250000000005</t>
+          <t>20251208173045000025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T21:06:16.932937</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2025-12-10T06:52:45.668942</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -1992,37 +1992,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-55-39-228-DR0O</t>
+          <t>DEI-2025-12-11-21-05-36-049-LtcH</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>T4121020250000000005</t>
+          <t>20251208173045000028</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T21:06:16.933335</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2025-12-10T06:56:25.709640</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -2039,37 +2039,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-49-43-953-pp5J</t>
+          <t>DEI-2025-12-10-06-15-14-417-x0do</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>T4121020250000000006</t>
+          <t>20251209162846000001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>NO DESTINATION FOUND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-10T06:15:45.491490</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2025-12-10T06:50:25.681059</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -2086,37 +2086,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-49-41-949-A6s3</t>
+          <t>DEI-2025-12-11-20-34-42-363-gmqg</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>T4121020250000000006</t>
+          <t>20251210221319000029</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:35:06.786258</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2025-12-10T06:50:25.683402</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -2133,37 +2133,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-52-02-856-OQBU</t>
+          <t>DEI-2025-12-11-21-04-39-531-SrHD</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>T4121020250000000006</t>
+          <t>20251210221319000031</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T21:05:16.928023</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2025-12-10T06:52:45.668942</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -2180,37 +2180,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-55-49-514-cHcu</t>
+          <t>DEI-2025-12-11-20-34-50-379-6VtJ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>T4121020250000000006</t>
+          <t>20251210221319000033</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:35:06.791323</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2025-12-10T06:56:25.710122</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -2227,37 +2227,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-49-45-109-1Z0O</t>
+          <t>DEI-2025-12-11-20-34-24-251-OwJu</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>T4121020250000000007</t>
+          <t>20251210221319000036</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:35:06.784945</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2025-12-10T06:50:25.681059</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -2274,37 +2274,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-49-47-121-HjhM</t>
+          <t>DEI-2025-12-11-20-34-48-756-PJaB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>T4121020250000000007</t>
+          <t>20251210221319000037</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:35:06.791323</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2025-12-10T06:50:25.683004</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -2321,37 +2321,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-52-05-998-Hzuw</t>
+          <t>DEI-2025-12-11-20-34-37-100-PyNf</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>T4121020250000000007</t>
+          <t>20251210221319000038</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:35:06.786258</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2025-12-10T06:52:45.669783</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -2368,37 +2368,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-55-42-267-e1NB</t>
+          <t>DEI-2025-12-11-21-04-44-192-iZmh</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>T4121020250000000007</t>
+          <t>20251210221319000039</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T21:05:16.928684</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2025-12-10T06:56:25.710122</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -2415,37 +2415,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-49-48-249-U0h1</t>
+          <t>DEI-2025-12-11-20-34-46-575-YYnS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>T4121020250000000008</t>
+          <t>20251210221319000040</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:35:06.789509</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2025-12-10T06:50:25.683004</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -2462,37 +2462,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-49-49-021-BjUl</t>
+          <t>DEI-2025-12-11-21-04-28-085-Nal1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>T4121020250000000008</t>
+          <t>20251210221319000043</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T21:05:16.926917</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2025-12-10T06:50:25.710870</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -2509,37 +2509,37 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-52-09-153-BuBK</t>
+          <t>DEI-2025-12-11-20-34-33-027-Kl2U</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>T4121020250000000008</t>
+          <t>20251210221319000044</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T20:35:06.784945</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2025-12-10T06:52:45.669783</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>
@@ -2556,37 +2556,178 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DEI-2025-12-10-06-55-50-769-fwPH</t>
+          <t>DEI-2025-12-11-21-04-52-470-vOSf</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>T4121020250000000008</t>
+          <t>20251210221319000045</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>2025-12-11T21:05:16.928684</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2025-12-10T06:56:25.709437</t>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-11-21-04-35-292-FPc5</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>20251210221319000046</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>GoodsholderDivertedDueToException</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2025-12-11T21:05:16.926069</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-11-21-04-37-887-mCzj</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>20251210221319000047</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>GoodsholderDivertedDueToException</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2025-12-11T21:05:16.926069</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-03-06-44-58-073-Wail</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>90251202191347000002</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>GoodsholderDivertedDueToException</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>NO DESTINATION FOUND</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2025-12-03T06:45:25.326921</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,12 +488,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-12-15-23-36-38-189-jAyG</t>
+          <t>DEI-2025-12-19-08-24-05-441-DxrT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20251215144828000001</t>
+          <t>00081121920253492500</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2025-12-15T23:37:24.362657</t>
+          <t>2025-12-19T08:24:51.327122</t>
         </is>
       </c>
     </row>
@@ -535,12 +535,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-12-15-23-36-39-023-cxtV</t>
+          <t>DEI-2025-12-19-08-24-06-134-3PCa</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20251215144828000001</t>
+          <t>00081121920253492500</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2025-12-15T23:37:24.362657</t>
+          <t>2025-12-19T08:24:51.327122</t>
         </is>
       </c>
     </row>
@@ -582,12 +582,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-12-15-23-36-45-186-SSSf</t>
+          <t>DEI-2025-12-19-08-24-18-058-Onsq</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20251215144828000001</t>
+          <t>00081121920253492500</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2025-12-15T23:37:24.362657</t>
+          <t>2025-12-19T08:24:51.427243</t>
         </is>
       </c>
     </row>
@@ -629,22 +629,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-12-15-23-36-59-816-MAei</t>
+          <t>DEI-2025-12-19-08-24-30-568-Gxu2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20251215144828000001</t>
+          <t>00081121920253492500</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DCI_DEI_RemoveConditionCode</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2025-12-15T23:37:24.364149</t>
+          <t>2025-12-19T08:24:51.489999</t>
         </is>
       </c>
     </row>
@@ -676,12 +676,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-12-15-23-36-52-214-mx21</t>
+          <t>DEI-2025-12-19-08-24-07-549-mM9b</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20251215144828000001</t>
+          <t>00081121920255149004</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -691,22 +691,1479 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.424144</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-10-845-Imo2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00081121920255149004</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.424313</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-20-062-Q5tS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00081121920255149004</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.453879</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-42-647-KRV1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00081121920255149004</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:25:21.292579</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-32-537-7198</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00081121920255149004</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>PutawayTaskResult</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2025-12-15T23:37:24.364463</t>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:25:21.292722</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-09-028-5ThP</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00081121920255540007</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.424313</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-12-231-IFfC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00081121920255540007</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.424313</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-21-603-ZR4d</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00081121920255540007</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.465759</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-34-023-PS2V</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00081121920255540007</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:25:21.292302</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-42-724-8qVW</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00081121920255540007</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:25:21.293398</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-06-666-hlWa</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00081121920255700701</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.326954</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-05-989-TiNZ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00081121920255700701</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.327122</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-18-565-yDdv</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00081121920255700701</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.427243</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-31-070-g4gE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00081121920255700701</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.489999</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-07-067-DEhD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00081121920255802103</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.424144</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-10-369-xTXa</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00081121920255802103</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.424313</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-19-556-LIdb</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00081121920255802103</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.447627</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-32-043-QbPm</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00081121920255802103</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:25:21.289847</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-08-064-dnh6</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00081121920257937905</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.424144</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-11-282-56Du</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00081121920257937905</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.424144</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-20-573-peWd</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00081121920257937905</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.456149</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-33-049-UNjZ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00081121920257937905</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:25:21.292722</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-42-768-shYG</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00081121920257937905</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:25:21.293398</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-11-792-cSRy</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00081121920258260606</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.420902</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-08-554-Jwdf</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00081121920258260606</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.424313</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-21-096-7Xoa</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00081121920258260606</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.456149</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-33-533-Y4YS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00081121920258260606</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:25:21.292722</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-42-685-VzTa</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>00081121920258260606</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:25:21.293398</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-06-529-SU6a</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>00081121920258346802</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.360508</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-09-670-9JNT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>00081121920258346802</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.424144</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-19-042-ljyE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>00081121920258346802</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.441533</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-19-08-24-31-567-LFQ9</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>00081121920258346802</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2025-12-19T08:24:51.489999</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,27 +451,27 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Lock</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Message_Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Created_on</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>RSN_CODE</t>
         </is>
       </c>
     </row>
@@ -488,37 +488,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-12-22-00-47-23-064-1Wh2</t>
+          <t>DEI-2025-12-25-01-39-46-817-HMzl</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20201222000000000001</t>
+          <t>20251224165006000001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GoodsholderDivertedDueToException</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-12-22T00:47:56.553551</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
+          <t>2025-12-25T01:40:27.733455</t>
         </is>
       </c>
     </row>
@@ -535,37 +535,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-12-18-02-55-32-751-l3yF</t>
+          <t>DEI-2025-12-25-01-39-45-905-f8bY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>T4000000000000012185</t>
+          <t>20251224165006000001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GoodsholderDivertedDueToException</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-12-18T02:56:07.948991</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
+          <t>2025-12-25T01:40:27.733705</t>
         </is>
       </c>
     </row>
@@ -582,37 +582,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-12-18-02-41-50-989-vnjM</t>
+          <t>DEI-2025-12-25-01-40-30-845-nfh8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T4000000000000012181</t>
+          <t>20251224165006000001</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GoodsholderDivertedDueToException</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>RoutingTaskResult</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-12-18T02:42:07.891082</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
+          <t>2025-12-25T01:41:17.708277</t>
         </is>
       </c>
     </row>
@@ -629,37 +629,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-12-18-00-19-54-316-dTN0</t>
+          <t>DEI-2025-12-25-02-01-52-269-3oqh</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TEST0000000000000001</t>
+          <t>20251224165006000001</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GoodsholderDivertedDueToException</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2025-12-18T00:20:29.858888</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
+          <t>2025-12-25T02:02:37.814417</t>
         </is>
       </c>
     </row>
@@ -676,37 +676,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-12-17-05-00-24-451-8mPi</t>
+          <t>DEI-2025-12-25-02-03-40-654-COW9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>T2251203181857000002</t>
+          <t>20251224165006000001</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GoodsholderDivertedDueToException</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2025-12-17T05:01:19.242064</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
+          <t>2025-12-25T02:04:27.820903</t>
         </is>
       </c>
     </row>
@@ -723,37 +723,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2025-12-17-04-05-05-857-rUbt</t>
+          <t>DEI-2025-12-25-02-04-41-839-WbaT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20251203004902000001</t>
+          <t>20251224165006000001</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2025-12-17T04:05:38.997936</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
+          <t>2025-12-25T02:05:27.831674</t>
         </is>
       </c>
     </row>
@@ -770,37 +770,272 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEI-2025-12-16-03-35-49-740-R5R2</t>
+          <t>DEI-2025-12-25-01-39-47-474-rtg0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20251208173045000009</t>
+          <t>20251224165006000002</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2025-12-25T01:40:27.733705</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-25-01-39-47-925-ifR4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20251224165006000002</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2025-12-25T01:40:27.733705</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-25-01-40-32-935-7u1P</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20251224165006000002</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2025-12-25T01:41:17.708277</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-25-02-01-54-308-qUN2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20251224165006000002</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2025-12-25T02:02:37.814417</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-25-02-03-43-688-tFPG</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20251224165006000002</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2025-12-25T02:04:27.820870</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-25-02-04-43-806-ydet</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20251224165006000002</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>GoodsholderDivertedDueToException</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2025-12-16T03:36:31.782541</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2025-12-25T02:05:27.831674</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,12 +488,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-12-25-01-39-46-817-HMzl</t>
+          <t>DEI-2026-01-15-22-38-23-514-qYjP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20251224165006000001</t>
+          <t>20260115140343000001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -503,22 +503,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2025-12-25T01:40:27.733455</t>
+          <t>2026-01-15T22:39:04.726146</t>
         </is>
       </c>
     </row>
@@ -535,12 +535,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-12-25-01-39-45-905-f8bY</t>
+          <t>DEI-2026-01-15-22-38-40-967-qwH0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20251224165006000001</t>
+          <t>20260115140343000001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2025-12-25T01:40:27.733705</t>
+          <t>2026-01-15T22:39:04.863494</t>
         </is>
       </c>
     </row>
@@ -582,12 +582,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-12-25-01-40-30-845-nfh8</t>
+          <t>DEI-2026-01-15-22-38-58-522-sKrI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20251224165006000001</t>
+          <t>20260115140343000001</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RoutingTaskResult</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -607,12 +607,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2025-12-25T01:41:17.708277</t>
+          <t>2026-01-15T22:39:44.482423</t>
         </is>
       </c>
     </row>
@@ -629,22 +629,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2025-12-25-02-01-52-269-3oqh</t>
+          <t>DEI-2026-01-15-22-39-17-310-J9Vt</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20251224165006000001</t>
+          <t>20260115140343000001</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>DCI_DEI_RemoveConditionCode</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2025-12-25T02:02:37.814417</t>
+          <t>2026-01-15T22:39:44.519233</t>
         </is>
       </c>
     </row>
@@ -676,12 +676,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2025-12-25-02-03-40-654-COW9</t>
+          <t>DEI-2026-01-15-22-38-24-657-Sjb2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20251224165006000001</t>
+          <t>20260115140343000002</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2025-12-25T02:04:27.820903</t>
+          <t>2026-01-15T22:39:04.728338</t>
         </is>
       </c>
     </row>
@@ -723,12 +723,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2025-12-25-02-04-41-839-WbaT</t>
+          <t>DEI-2026-01-15-22-38-29-396-jjBK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20251224165006000001</t>
+          <t>20260115140343000002</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GoodsholderDivertedDueToException</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2025-12-25T02:05:27.831674</t>
+          <t>2026-01-15T22:39:04.765549</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEI-2025-12-25-01-39-47-474-rtg0</t>
+          <t>DEI-2026-01-15-22-38-42-076-A6Xg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20251224165006000002</t>
+          <t>20260115140343000002</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -795,12 +795,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2025-12-25T01:40:27.733705</t>
+          <t>2026-01-15T22:39:04.863537</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEI-2025-12-25-01-39-47-925-ifR4</t>
+          <t>DEI-2026-01-15-22-38-59-419-rHt2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20251224165006000002</t>
+          <t>20260115140343000002</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2025-12-25T01:40:27.733705</t>
+          <t>2026-01-15T22:39:44.488237</t>
         </is>
       </c>
     </row>
@@ -864,22 +864,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DEI-2025-12-25-01-40-32-935-7u1P</t>
+          <t>DEI-2026-01-15-22-39-17-218-dkwA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20251224165006000002</t>
+          <t>20260115140343000002</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RoutingTaskResult</t>
+          <t>DCI_DEI_RemoveConditionCode</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2025-12-25T01:41:17.708277</t>
+          <t>2026-01-15T22:39:44.519233</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DEI-2025-12-25-02-01-54-308-qUN2</t>
+          <t>DEI-2026-01-15-22-38-25-692-bgjR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20251224165006000002</t>
+          <t>20260115140343000003</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2025-12-25T02:02:37.814417</t>
+          <t>2026-01-15T22:39:04.728338</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DEI-2025-12-25-02-03-43-688-tFPG</t>
+          <t>DEI-2026-01-15-22-38-30-634-GW1c</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20251224165006000002</t>
+          <t>20260115140343000003</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2025-12-25T02:04:27.820870</t>
+          <t>2026-01-15T22:39:04.785672</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DEI-2025-12-25-02-04-43-806-ydet</t>
+          <t>DEI-2026-01-15-22-38-43-082-vRvP</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20251224165006000002</t>
+          <t>20260115140343000003</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GoodsholderDivertedDueToException</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1030,12 +1030,1234 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2025-12-25T02:05:27.831674</t>
+          <t>2026-01-15T22:39:04.863537</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-39-00-259-geUT</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20260115140343000003</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:44.488237</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-39-17-353-i5S1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20260115140343000003</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:44.528664</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-26-618-RvMj</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20260115140343000004</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.765314</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-31-792-omwU</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20260115140343000004</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.785672</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-44-096-Rx7v</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20260115140343000004</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.863537</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-39-01-210-IfPf</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20260115140343000004</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:44.487475</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-27-578-cspV</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20260115140343000005</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.765314</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-32-549-1Yfu</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20260115140343000005</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.792997</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-45-036-2R1n</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>20260115140343000005</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.865661</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-39-02-229-BaXw</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>20260115140343000005</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:44.528664</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-28-511-N0GV</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>20260115140343000006</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.785672</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-33-438-NKtU</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>20260115140343000006</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.792997</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-45-952-IjzV</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>20260115140343000006</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.862075</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-39-03-142-P7nv</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>20260115140343000006</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:44.528664</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-29-493-XZgm</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>20260115140343000007</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.791622</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-34-332-t2Kw</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>20260115140343000007</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.809614</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-46-918-Nv99</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>20260115140343000007</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.862075</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-39-04-065-8bHg</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>20260115140343000007</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:44.528664</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-30-448-CW25</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>20260115140343000008</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.791622</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-35-370-3Hai</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>20260115140343000008</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.809614</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-47-835-ou0o</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>20260115140343000008</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.863529</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-39-05-041-O7g5</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>20260115140343000008</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:44.487475</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-31-510-ctFG</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>20260115140343000009</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.791622</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-36-191-WvZv</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>20260115140343000009</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.848195</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-38-48-730-BifP</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>20260115140343000009</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:04.871344</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-15-22-39-05-982-t0g1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>20260115140343000009</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-01-15T22:39:44.487475</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,12 +488,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-23-514-qYjP</t>
+          <t>DEI-2026-01-21-00-21-05-503-qGli</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20260115140343000001</t>
+          <t>00081012020261953401</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.726146</t>
+          <t>2026-01-21T00:21:48.355896</t>
         </is>
       </c>
     </row>
@@ -535,12 +535,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-40-967-qwH0</t>
+          <t>DEI-2026-01-21-00-21-07-650-DGc7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20260115140343000001</t>
+          <t>00081012020261953401</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.863494</t>
+          <t>2026-01-21T00:21:48.355896</t>
         </is>
       </c>
     </row>
@@ -582,12 +582,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-58-522-sKrI</t>
+          <t>DEI-2026-01-21-00-21-20-885-5UhX</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20260115140343000001</t>
+          <t>00081012020261953401</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:44.482423</t>
+          <t>2026-01-21T00:21:48.451791</t>
         </is>
       </c>
     </row>
@@ -629,22 +629,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-39-17-310-J9Vt</t>
+          <t>DEI-2026-01-21-00-21-36-391-KDU8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20260115140343000001</t>
+          <t>00081012020261953401</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DCI_DEI_RemoveConditionCode</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:44.519233</t>
+          <t>2026-01-21T00:22:18.336787</t>
         </is>
       </c>
     </row>
@@ -676,27 +676,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-24-657-Sjb2</t>
+          <t>DEI-2026-01-21-00-21-50-951-V0Lh</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20260115140343000002</t>
+          <t>00081012020261953401</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>DCI_DEI_RemoveConditionCode</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.728338</t>
+          <t>2026-01-21T00:22:18.370593</t>
         </is>
       </c>
     </row>
@@ -723,12 +723,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-29-396-jjBK</t>
+          <t>DEI-2026-01-21-00-21-04-611-4E2N</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20260115140343000002</t>
+          <t>00081012020263032300</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.765549</t>
+          <t>2026-01-21T00:21:48.352915</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-42-076-A6Xg</t>
+          <t>DEI-2026-01-21-00-21-05-461-Fmsf</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20260115140343000002</t>
+          <t>00081012020263032300</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.863537</t>
+          <t>2026-01-21T00:21:48.353834</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-59-419-rHt2</t>
+          <t>DEI-2026-01-21-00-21-20-092-oPGW</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20260115140343000002</t>
+          <t>00081012020263032300</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:44.488237</t>
+          <t>2026-01-21T00:21:48.451791</t>
         </is>
       </c>
     </row>
@@ -864,22 +864,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-39-17-218-dkwA</t>
+          <t>DEI-2026-01-21-00-21-35-562-CZP6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20260115140343000002</t>
+          <t>00081012020263032300</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DCI_DEI_RemoveConditionCode</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:44.519233</t>
+          <t>2026-01-21T00:22:18.336787</t>
         </is>
       </c>
     </row>
@@ -911,27 +911,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-25-692-bgjR</t>
+          <t>DEI-2026-01-21-00-21-51-183-yxDp</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20260115140343000003</t>
+          <t>00081012020263032300</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>DCI_DEI_RemoveConditionCode</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.728338</t>
+          <t>2026-01-21T00:22:18.370593</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-30-634-GW1c</t>
+          <t>DEI-2026-01-21-00-21-08-291-iAqB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20260115140343000003</t>
+          <t>00081012020263388102</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.785672</t>
+          <t>2026-01-21T00:21:48.358920</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-43-082-vRvP</t>
+          <t>DEI-2026-01-21-00-21-06-293-ev0q</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20260115140343000003</t>
+          <t>00081012020263388102</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.863537</t>
+          <t>2026-01-21T00:21:48.376685</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-39-00-259-geUT</t>
+          <t>DEI-2026-01-21-00-21-21-678-eGyB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20260115140343000003</t>
+          <t>00081012020263388102</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:44.488237</t>
+          <t>2026-01-21T00:21:48.453296</t>
         </is>
       </c>
     </row>
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-39-17-353-i5S1</t>
+          <t>DEI-2026-01-21-00-21-37-197-Rpu8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20260115140343000003</t>
+          <t>00081012020263388102</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DCI_DEI_RemoveConditionCode</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:44.528664</t>
+          <t>2026-01-21T00:22:18.339056</t>
         </is>
       </c>
     </row>
@@ -1146,27 +1146,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-26-618-RvMj</t>
+          <t>DEI-2026-01-21-00-21-51-220-rHQS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20260115140343000004</t>
+          <t>00081012020263388102</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>DCI_DEI_RemoveConditionCode</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.765314</t>
+          <t>2026-01-21T00:22:18.370593</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-31-792-omwU</t>
+          <t>DEI-2026-01-21-00-21-10-459-627Z</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20260115140343000004</t>
+          <t>00081012020263760707</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.785672</t>
+          <t>2026-01-21T00:21:48.433226</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-44-096-Rx7v</t>
+          <t>DEI-2026-01-21-00-21-11-383-g94s</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20260115140343000004</t>
+          <t>00081012020263760707</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.863537</t>
+          <t>2026-01-21T00:21:48.433226</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-39-01-210-IfPf</t>
+          <t>DEI-2026-01-21-00-21-25-829-51ct</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20260115140343000004</t>
+          <t>00081012020263760707</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:44.487475</t>
+          <t>2026-01-21T00:21:48.456673</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-27-578-cspV</t>
+          <t>DEI-2026-01-21-00-21-41-266-jUXR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20260115140343000005</t>
+          <t>00081012020263760707</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.765314</t>
+          <t>2026-01-21T00:22:18.344157</t>
         </is>
       </c>
     </row>
@@ -1381,27 +1381,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-32-549-1Yfu</t>
+          <t>DEI-2026-01-21-00-21-51-047-FfX7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20260115140343000005</t>
+          <t>00081012020263760707</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>DCI_DEI_RemoveConditionCode</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.792997</t>
+          <t>2026-01-21T00:22:18.370593</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-45-036-2R1n</t>
+          <t>DEI-2026-01-21-00-21-08-778-Oapz</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20260115140343000005</t>
+          <t>00081012020263893305</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.865661</t>
+          <t>2026-01-21T00:21:48.412732</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-39-02-229-BaXw</t>
+          <t>DEI-2026-01-21-00-21-10-106-T9nq</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20260115140343000005</t>
+          <t>00081012020263893305</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1490,12 +1490,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:44.528664</t>
+          <t>2026-01-21T00:21:48.412732</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-28-511-N0GV</t>
+          <t>DEI-2026-01-21-00-21-24-117-SaMJ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20260115140343000006</t>
+          <t>00081012020263893305</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.785672</t>
+          <t>2026-01-21T00:21:48.453710</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-33-438-NKtU</t>
+          <t>DEI-2026-01-21-00-21-39-658-R5az</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20260115140343000006</t>
+          <t>00081012020263893305</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.792997</t>
+          <t>2026-01-21T00:22:18.344157</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-45-952-IjzV</t>
+          <t>DEI-2026-01-21-00-21-10-699-uypz</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20260115140343000006</t>
+          <t>00081012020266921006</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.862075</t>
+          <t>2026-01-21T00:21:48.413314</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-39-03-142-P7nv</t>
+          <t>DEI-2026-01-21-00-21-09-588-agF2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>20260115140343000006</t>
+          <t>00081012020266921006</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:44.528664</t>
+          <t>2026-01-21T00:21:48.419787</t>
         </is>
       </c>
     </row>
@@ -1710,12 +1710,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-29-493-XZgm</t>
+          <t>DEI-2026-01-21-00-21-25-006-pVJv</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20260115140343000007</t>
+          <t>00081012020266921006</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.791622</t>
+          <t>2026-01-21T00:21:48.453710</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-34-332-t2Kw</t>
+          <t>DEI-2026-01-21-00-21-40-467-cmfB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20260115140343000007</t>
+          <t>00081012020266921006</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.809614</t>
+          <t>2026-01-21T00:22:18.344157</t>
         </is>
       </c>
     </row>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-46-918-Nv99</t>
+          <t>DEI-2026-01-21-00-21-08-889-YbHQ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20260115140343000007</t>
+          <t>00081012020267472103</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.862075</t>
+          <t>2026-01-21T00:21:48.404662</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-39-04-065-8bHg</t>
+          <t>DEI-2026-01-21-00-21-07-091-rRBf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20260115140343000007</t>
+          <t>00081012020267472103</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:44.528664</t>
+          <t>2026-01-21T00:21:48.410443</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-30-448-CW25</t>
+          <t>DEI-2026-01-21-00-21-22-510-BPwt</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20260115140343000008</t>
+          <t>00081012020267472103</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.791622</t>
+          <t>2026-01-21T00:21:48.452572</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-35-370-3Hai</t>
+          <t>DEI-2026-01-21-00-21-38-005-7ylb</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20260115140343000008</t>
+          <t>00081012020267472103</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.809614</t>
+          <t>2026-01-21T00:22:18.340075</t>
         </is>
       </c>
     </row>
@@ -1992,27 +1992,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-47-835-ou0o</t>
+          <t>DEI-2026-01-21-00-21-50-998-iyKa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20260115140343000008</t>
+          <t>00081012020267472103</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>DCI_DEI_RemoveConditionCode</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.863529</t>
+          <t>2026-01-21T00:22:18.361728</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-39-05-041-O7g5</t>
+          <t>DEI-2026-01-21-00-21-11-246-T6AT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20260115140343000008</t>
+          <t>00081012020267722608</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PutawayTaskResult</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:44.487475</t>
+          <t>2026-01-21T00:21:48.445171</t>
         </is>
       </c>
     </row>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-31-510-ctFG</t>
+          <t>DEI-2026-01-21-00-21-11-959-uhoy</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>20260115140343000009</t>
+          <t>00081012020267722608</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.791622</t>
+          <t>2026-01-21T00:21:48.445171</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-36-191-WvZv</t>
+          <t>DEI-2026-01-21-00-21-26-649-0Eyj</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20260115140343000009</t>
+          <t>00081012020267722608</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.848195</t>
+          <t>2026-01-21T00:21:48.456673</t>
         </is>
       </c>
     </row>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-38-48-730-BifP</t>
+          <t>DEI-2026-01-21-00-21-42-070-P7zY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20260115140343000009</t>
+          <t>00081012020267722608</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GoodsholderMeasured</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-01-15T22:39:04.871344</t>
+          <t>2026-01-21T00:22:18.343637</t>
         </is>
       </c>
     </row>
@@ -2227,12 +2227,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DEI-2026-01-15-22-39-05-982-t0g1</t>
+          <t>DEI-2026-01-21-00-21-09-460-9LhS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>20260115140343000009</t>
+          <t>00081012020269357704</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2242,22 +2242,210 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-01-21T00:21:48.404662</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-21-00-21-07-929-MN1C</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>00081012020269357704</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-01-21T00:21:48.410443</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-21-00-21-23-302-4pFS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>00081012020269357704</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-01-21T00:21:48.454236</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-21-00-21-38-855-d3RT</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>00081012020269357704</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>PutawayTaskResult</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-01-15T22:39:44.487475</t>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-01-21T00:22:18.344157</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DEI-2026-01-21-00-21-51-137-lB6i</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>00081012020269357704</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-01-21T00:22:18.370593</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:I161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,35 +451,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Lock</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Message_Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>ReasonCode</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>VendorCodeDesc</t>
+          <t>User</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>DivertedLocation</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Created_on</t>
         </is>
@@ -498,35 +488,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2026-01-27-10-20-21-758-RXaX</t>
+          <t>DEI-2026-02-10-14-11-54-028-Oytp</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00000010810000000549</t>
+          <t>00015009940000834944</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PPK_DEI_TaskRelease</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>system-msg-user@1081</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-01-27T10:21:02.922905</t>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:12:43.703113</t>
         </is>
       </c>
     </row>
@@ -543,35 +535,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2026-01-27-10-25-40-246-ph8o</t>
+          <t>DEI-2026-02-10-14-11-55-065-cBQf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00000010810000000549</t>
+          <t>00015009940000834944</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PPK_DEI_PickingFeedback</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-01-27T10:26:22.987816</t>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:12:43.703113</t>
         </is>
       </c>
     </row>
@@ -588,35 +582,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2026-01-27-10-25-38-440-8GU2</t>
+          <t>DEI-2026-02-10-14-14-22-625-dJcd</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00000010810000000549</t>
+          <t>00015009940000834944</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RetrievalTaskResult</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-01-27T10:26:22.989799</t>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:15:03.724084</t>
         </is>
       </c>
     </row>
@@ -633,47 +629,7369 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2026-01-27-10-32-58-171-W9Cr</t>
+          <t>DEI-2026-02-10-14-19-43-507-31EB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00000010810000000549</t>
+          <t>00015009940000834944</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PackTaskResult</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>PutawayTaskResult</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Task maintenance by WCS</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5901000000</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-01-27T10:33:42.997161</t>
+          <t>2026-02-10T14:20:23.730718</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-590-F5Ao</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00015009940000834944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.094622</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-13-10-382-cjnl</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00015009940000834951</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:13:53.699388</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-13-09-803-xLUQ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00015009940000834951</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:13:53.699658</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-15-38-887-8cVD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00015009940000834951</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:16:23.705329</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-20-47-829-0yKQ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00015009940000834951</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:21:33.745630</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-883-jwDO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00015009940000834951</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.154627</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-13-47-799-bhhb</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00015009940000834968</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:14:33.719641</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-13-48-260-JrMz</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00015009940000834968</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:14:33.719641</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-16-16-701-2RpU</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00015009940000834968</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:17:03.715323</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-21-41-253-gACD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00015009940000834968</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:03.755383</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-294-sUDW</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00015009940000834968</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.054603</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-20-02-028-mSQe</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00015009940000834975</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:20:23.732315</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-20-02-707-wEiv</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00015009940000834975</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:20:23.732315</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-22-31-152-5yjY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00015009940000834975</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:23:13.745063</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-27-44-586-dGRE</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00015009940000834975</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:28:33.760143</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-550-MDAQ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00015009940000834975</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.094622</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-20-13-659-ullu</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00015009940000834982</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:20:53.734110</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-20-14-194-sxYq</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00015009940000834982</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:20:53.734110</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-22-43-125-TkI7</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00015009940000834982</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:23:13.749339</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-27-55-346-hcT8</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00015009940000834982</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:28:33.760143</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-637-znav</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00015009940000834982</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.094622</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-20-25-442-BkqF</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00015009940000834999</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:20:53.735793</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-20-25-885-E792</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00015009940000834999</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:20:53.735793</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-22-55-234-Jfk3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00015009940000834999</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:23:13.750526</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-29-09-694-Ed2d</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00015009940000834999</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:29:43.787133</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-073-ZLPp</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00015009940000834999</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.054603</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-20-35-949-c9Jc</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00015009940000835002</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:20:53.737704</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-20-36-447-jqyK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>00015009940000835002</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:20:53.737704</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-23-04-946-ixzw</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>00015009940000835002</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:23:53.740994</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-28-28-946-0gTl</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>00015009940000835002</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:29:13.763962</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-499-QkGR</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>00015009940000835002</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.053266</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-20-48-248-bE4d</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>00015009940000835019</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:21:33.743396</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-20-47-749-JxRv</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>00015009940000835019</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:21:33.745630</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-23-17-070-HyIO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>00015009940000835019</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:23:53.741661</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-28-30-169-3XfM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>00015009940000835019</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:29:13.764427</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-685-4HKm</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>00015009940000835019</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.152285</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-21-00-156-3sI0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>00015009940000835026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:21:33.745360</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-20-59-744-NnvF</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>00015009940000835026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:21:33.746177</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-23-29-030-6JSu</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>00015009940000835026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:23:53.741661</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-28-41-439-7gzX</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>00015009940000835026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:29:13.762568</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-47-012-xpeH</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>00015009940000835026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.148106</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-21-09-866-73CE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>00015009940000835033</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:21:33.749055</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-21-10-294-vJ0E</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>00015009940000835033</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:21:33.749055</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-23-39-502-bNGn</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>00015009940000835033</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:24:23.744180</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-28-59-587-eog5</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>00015009940000835033</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:29:43.784244</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-034-MNcw</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>00015009940000835033</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.056301</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-21-20-017-rTHM</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>00015009940000835040</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:03.755032</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-21-20-442-6jdv</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>00015009940000835040</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:03.755032</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-23-49-363-wwaG</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>00015009940000835040</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:24:23.744180</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-29-06-384-svRn</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>00015009940000835040</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:29:43.785327</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-422-Ye5I</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>00015009940000835040</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.058691</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-21-29-997-w8ak</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>00015009940000835057</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:03.755032</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-21-30-417-Riis</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>00015009940000835057</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:03.755358</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-23-59-339-1EYc</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>00015009940000835057</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:24:23.744180</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-29-07-929-eqzD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>00015009940000835057</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:29:43.787133</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-766-e99f</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>00015009940000835057</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.154627</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-21-37-998-ls3N</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>00015009940000835064</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:03.757832</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-21-38-420-QXIN</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>00015009940000835064</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:03.757832</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-24-07-561-Cvl4</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>00015009940000835064</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:24:23.744180</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-29-31-744-dcCu</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>00015009940000835064</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:30:13.773114</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-924-QG6J</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>00015009940000835064</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.149898</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-21-48-438-8mLl</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>00015009940000835071</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:03.774207</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-21-48-004-QCET</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>00015009940000835071</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:03.779692</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-24-17-157-RvPN</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>00015009940000835071</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:25:03.766819</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-29-30-935-NqTK</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>00015009940000835071</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:30:13.775297</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-333-D5P7</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>00015009940000835071</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.058691</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-21-56-078-dc9J</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>00015009940000835088</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:43.741990</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-21-56-517-HPAd</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>00015009940000835088</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:43.741995</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-24-25-058-aflk</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>00015009940000835088</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:25:03.766819</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-29-38-384-rzYO</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>00015009940000835088</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:30:13.777195</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-47-109-5sw3</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>00015009940000835088</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.148106</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-22-06-543-5y5Z</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>00015009940000835095</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:43.747689</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-22-06-979-knAT</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>00015009940000835095</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:43.747689</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-24-35-562-7JI8</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>00015009940000835095</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:25:03.764647</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-30-46-162-uODx</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>00015009940000835095</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:31:33.776485</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-47-065-dnQB</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>00015009940000835095</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.148106</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-22-16-709-v6bk</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>00015009940000835101</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:43.748137</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-22-17-180-HbAo</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>00015009940000835101</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:43.748137</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-24-45-577-8Lds</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>00015009940000835101</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:25:03.766098</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-30-11-314-jfJi</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>00015009940000835101</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:30:53.779514</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-809-mdEh</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>00015009940000835101</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.154627</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-22-24-593-zOiz</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>00015009940000835118</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:43.766011</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-22-25-036-yy1a</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>00015009940000835118</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:22:43.766011</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-24-54-126-LZxU</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>00015009940000835118</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:25:43.748344</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-30-08-357-yRe1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>00015009940000835118</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:30:53.778997</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-844-pk1J</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>00015009940000835118</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.154627</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-22-34-732-lBaQ</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>00015009940000835125</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:23:13.751834</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-22-35-161-zILc</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>00015009940000835125</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:23:13.751834</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-25-04-062-Ofvh</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>00015009940000835125</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:25:43.748344</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-30-17-279-pHyU</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>00015009940000835125</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:30:53.779514</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-734-KnZa</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>00015009940000835125</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.152285</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-22-42-996-p63f</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>00015009940000835132</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:23:13.749339</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-22-43-366-h2A2</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>00015009940000835132</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:23:13.749339</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-25-11-787-Pj4z</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>00015009940000835132</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:25:43.747433</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-14-30-33-263-N0oD</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>00015009940000835132</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-02-10T14:30:53.780298</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-37-46-964-ckLd</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>00015009940000835132</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:38:32.149898</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-18-46-932-Y8Z7</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>20260202181148000001</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:19:28.199362</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-18-48-045-LjYN</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>20260202181148000001</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:19:28.199362</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-21-16-009-EoVn</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>20260202181148000001</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:21:58.173165</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-26-39-625-ucJ3</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>20260202181148000001</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:27:18.195779</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-35-50-258-16Rs</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>20260202181148000001</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:36:32.047545</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-18-48-543-pYLO</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>20260202181148000002</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:19:28.198760</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-18-50-133-CfGb</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>20260202181148000002</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:19:28.200832</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-21-18-321-e2u0</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>20260202181148000002</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:21:58.173165</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-26-29-178-62I9</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>20260202181148000002</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:27:18.198342</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-35-51-062-SRiA</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>20260202181148000002</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:36:32.047078</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-18-50-948-Tb9k</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>20260202181148000003</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:19:28.203759</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-18-51-453-6HEM</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>20260202181148000003</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:19:28.203759</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-21-20-234-aHDS</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>20260202181148000003</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:21:58.174293</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-26-32-876-99BF</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>20260202181148000003</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:27:18.198342</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-35-50-003-NzYE</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>20260202181148000003</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:36:32.044632</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-18-53-201-wwHw</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>20260202181148000004</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:19:28.222969</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-18-53-666-pl9F</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>20260202181148000004</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:19:28.222969</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-21-22-578-mORB</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>20260202181148000004</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:21:58.174293</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-26-36-268-8WrD</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>20260202181148000004</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:27:18.195779</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-35-50-361-6OLy</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>20260202181148000004</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:36:32.047545</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-18-55-133-hcoc</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>20260202181148000005</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:19:28.246810</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-18-55-623-l9O6</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>20260202181148000005</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:19:28.246810</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-21-23-720-e7KT</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>20260202181148000005</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:21:58.172354</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-26-42-485-biQf</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>20260202181148000005</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:27:18.197479</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-35-50-999-L599</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>20260202181148000005</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:36:32.048829</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-18-57-320-Cmdn</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>20260202181148000006</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:19:28.247178</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-18-57-829-MH8j</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>20260202181148000006</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:19:28.247178</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-21-25-943-rGrg</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>20260202181148000006</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:21:58.171997</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-26-45-845-iOa7</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>20260202181148000006</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:27:18.197479</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-35-50-684-hTDF</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>20260202181148000006</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:36:32.043783</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-27-22-571-pLjH</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>20260202181148000007</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:28:08.212354</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-27-21-983-beId</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>20260202181148000007</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:28:08.215270</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-29-50-330-Fyaz</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>20260202181148000007</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:30:38.214175</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-36-09-854-NNUt</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>20260202181148000007</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:36:58.236397</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-35-50-840-f3nl</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>20260202181148000007</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:36:32.048829</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-27-23-585-GEU9</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>20260202181148000008</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:28:08.215383</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-27-24-271-vlJK</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>20260202181148000008</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:28:08.215383</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-29-52-518-JdSY</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>20260202181148000008</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:30:38.214175</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-35-01-121-n90l</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>20260202181148000008</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:35:48.232752</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-35-50-633-epB0</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>20260202181148000008</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:36:32.043783</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-27-25-291-XdCX</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>20260202181148000009</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:28:08.219813</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-27-25-728-yAxx</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>20260202181148000009</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:28:08.219813</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-29-54-828-YjEp</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>20260202181148000009</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:30:38.214177</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-35-12-359-jbhN</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>20260202181148000009</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:35:48.236897</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-35-50-181-EIGw</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>20260202181148000009</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:36:32.044632</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-27-28-013-Sj3I</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>20260202181148000010</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:28:08.217634</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-27-28-471-qHQB</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>20260202181148000010</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:28:08.217634</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-29-56-557-mqNX</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>20260202181148000010</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:30:38.214177</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-35-16-378-YI8N</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>20260202181148000010</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:35:48.235645</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-35-50-767-zSf0</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>20260202181148000010</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:36:32.045690</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-27-29-849-oVHs</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>20260202181148000011</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:28:08.280215</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-27-30-312-FwDv</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>20260202181148000011</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:28:08.280215</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-29-58-764-3pML</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>20260202181148000011</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:30:38.214175</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-35-22-902-OjIp</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>20260202181148000011</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:35:48.235645</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-35-50-453-HT9K</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>20260202181148000011</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:36:32.043783</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-27-31-688-SxgW</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>20260202181148000012</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:28:08.279642</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-27-32-219-ASa0</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>20260202181148000012</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:28:08.279642</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-30-00-566-BeYo</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>20260202181148000012</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:30:38.215949</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-10-03-35-09-582-prIr</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>20260202181148000012</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>2026-02-10T03:35:48.236897</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>DEI-2026-02-11-14-35-50-925-eSMX</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>20260202181148000012</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>DCI_DEI_RemoveConditionCode</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>2026-02-11T14:36:32.048829</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,12 +488,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2026-03-05-14-22-00-345-y1bM</t>
+          <t>DEI-2026-03-20-00-14-27-911-Tj0N</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20260202093747000000</t>
+          <t>20260318210346000001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -503,22 +503,3735 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.787201</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-25-126-cmlg</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>20260318210346000001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>GoodsholderAnnounced</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>NO DESTINATION FOUND</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-03-05T14:22:19.206969</t>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.793466</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-16-54-212-uaun</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>20260318210346000001</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.700530</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-54-335-fk3o</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20260318210346000001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.710381</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-28-717-EkNC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20260318210346000002</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.787201</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-26-942-pc4y</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20260318210346000002</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.793466</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-16-56-387-YsLj</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20260318210346000002</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.699921</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-57-170-db2q</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20260318210346000002</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.710381</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-28-925-Ol90</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20260318210346000003</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.793466</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-30-224-wF5g</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20260318210346000003</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.793466</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-16-57-970-rIri</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20260318210346000003</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.703136</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-58-800-Emvt</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20260318210346000003</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.710992</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-31-759-qUYx</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20260318210346000004</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.783152</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-31-235-NaZq</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20260318210346000004</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.786705</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-00-626-iv8j</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20260318210346000004</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.703136</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-00-461-qIeI</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20260318210346000004</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.710992</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-32-894-iLbe</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20260318210346000005</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.890177</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-33-462-S3Ya</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20260318210346000005</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.890177</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-02-272-kfQ5</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20260318210346000005</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.699810</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-02-575-UKgl</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20260318210346000005</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.710992</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-35-455-AaO1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>20260318210346000006</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.831637</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-34-987-JeAw</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>20260318210346000006</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.837437</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-04-371-nUwt</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>20260318210346000006</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.705855</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-04-748-OAsG</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>20260318210346000006</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.710864</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-37-231-wPht</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>20260318210346000007</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.847172</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-37-784-m1cq</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>20260318210346000007</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.847172</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-05-986-z7IX</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>20260318210346000007</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.705855</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-06-851-tEs3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>20260318210346000007</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.712174</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-39-755-b2jc</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>20260318210346000008</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.890151</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-39-199-gYZZ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>20260318210346000008</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.897298</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-08-148-cGjj</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>20260318210346000008</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.705666</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-08-515-Tzi5</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>20260318210346000008</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.712174</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-41-788-G4wr</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>20260318210346000009</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.906239</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-42-267-CbmM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>20260318210346000009</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.906239</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-10-815-eLcy</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>20260318210346000009</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.705666</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-10-870-yJEd</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>20260318210346000009</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.712428</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-44-195-GxQ8</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>20260318210346000010</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.921127</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-43-720-wNZt</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>20260318210346000010</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.925974</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-12-663-7OJ8</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>20260318210346000010</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.703029</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-13-066-CwcC</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>20260318210346000010</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.712428</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-45-479-ybMO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>20260318210346000011</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.939584</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-45-899-Hbvt</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>20260318210346000011</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.939584</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-14-836-n3rE</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>20260318210346000011</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.703029</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-15-673-tkeP</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>20260318210346000011</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.763506</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-48-551-6HP5</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>20260318210346000012</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.941939</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-48-112-pluA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>20260318210346000012</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.955882</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-16-931-G8Q3</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>20260318210346000012</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.706465</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-17-359-dj0B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>20260318210346000012</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.765247</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-49-754-TzNc</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>20260318210346000013</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.970957</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-50-197-m51T</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>20260318210346000013</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.970957</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-18-573-j5g0</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>20260318210346000013</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.751913</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-19-594-uiWa</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>20260318210346000013</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.765247</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-54-017-CGKp</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>20260318210346000014</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:06.996144</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-52-030-Ihci</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>20260318210346000014</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:07.003531</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-21-728-4Flu</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>20260318210346000014</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.751913</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-21-697-QV5w</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>20260318210346000014</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.762885</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-54-130-fUk4</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>20260318210346000015</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:36.707195</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-54-915-FM3G</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>20260318210346000015</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:36.707195</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-23-330-M1En</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>20260318210346000015</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:17:36.743789</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-23-702-bQvx</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>20260318210346000015</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:36.762851</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-56-124-RNJQ</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>20260318210346000016</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:36.708185</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-56-681-LPvl</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>20260318210346000016</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:36.708185</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-25-485-iyQn</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>20260318210346000016</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:06.687071</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-25-343-2UK2</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>20260318210346000016</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:19:06.695733</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-58-353-FHW8</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>20260318210346000017</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:36.708500</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-14-58-970-LwOV</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>20260318210346000017</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:36.708500</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-27-085-5Fun</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>20260318210346000017</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:06.688742</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-27-492-Ejq4</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>20260318210346000017</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:19:06.698425</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-15-00-368-dn3j</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>20260318210346000018</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:36.708476</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-15-01-054-fzzo</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>20260318210346000018</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:36.708476</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-29-251-s4J4</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>20260318210346000018</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:06.688742</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-29-945-uQBR</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>20260318210346000018</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:19:06.698425</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-15-02-420-QtH6</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>20260318210346000019</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:36.736159</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-15-03-071-XbKq</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>20260318210346000019</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:36.736159</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-31-434-klL3</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>20260318210346000019</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:06.685537</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-31-554-bNib</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>20260318210346000019</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:19:06.696391</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-15-04-446-bVIn</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>20260318210346000020</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:36.749221</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-15-05-437-at7p</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>20260318210346000020</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:15:36.749221</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-17-33-584-lOV8</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>20260318210346000020</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:18:06.685537</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DEI-2026-03-20-00-18-33-755-XBDa</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>20260318210346000020</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:19:06.696391</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/J30/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,12 +488,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2026-06-29-02-27-36-095-RPKC</t>
+          <t>DEI-2026-07-29-13-07-26-803-saQH</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081062920260003101</t>
+          <t>00000010379092983216</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -513,12 +513,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>asure2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-29T02:28:18.796591</t>
+          <t>2026-07-29T13:08:15.492036</t>
         </is>
       </c>
     </row>
@@ -535,12 +535,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2026-06-29-02-27-46-732-9Nqp</t>
+          <t>DEI-2026-07-29-13-07-30-053-owOQ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081062920260003101</t>
+          <t>00000010379092983216</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderMeasured</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>asure2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-06-29T02:28:18.800368</t>
+          <t>2026-07-29T13:08:15.492036</t>
         </is>
       </c>
     </row>
@@ -582,12 +582,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2026-06-29-02-27-36-480-cPeH</t>
+          <t>DEI-2026-07-29-13-07-32-056-Lihh</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00081062920260003102</t>
+          <t>00000010379092983216</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GoodsholderAnnounced</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -607,12 +607,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>asure2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-06-29T02:28:18.800368</t>
+          <t>2026-07-29T13:08:15.492079</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEI-2026-06-29-02-27-48-016-WO9z</t>
+          <t>DEI-2026-07-29-13-27-41-811-Zckl</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00081062920260003102</t>
+          <t>00000010379092983216</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -644,22 +644,210 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-07-29T13:28:25.565806</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEI-2026-07-29-13-07-29-272-z4Sg</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00000010585288239549</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>asure2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-07-29T13:08:15.492036</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEI-2026-07-29-13-07-25-990-DXHJ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00000010585288239549</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-07-29T13:14:05.506055</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEI-2026-07-29-13-13-20-939-MNJn</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00000010585288239549</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-29T02:28:18.803171</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-07-29T13:14:05.506145</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEI-2026-07-29-13-27-40-884-BZQ3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00000010585288239549</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-07-29T13:28:25.566131</t>
         </is>
       </c>
     </row>
